--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C23BF-B6A9-4EF2-ACEB-8B2FEDDD5912}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E125BA-9DCD-4BC6-B7F9-EE7FBD92693B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AT$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AV$93</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="391">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1207,7 +1208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1271,6 +1272,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1365,7 +1373,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1742,12 +1750,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3C78D8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF3C78D8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF3C78D8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3C78D8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF3C78D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3C78D8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF3C78D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2144,12 +2242,38 @@
     <xf numFmtId="49" fontId="1" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <border>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2637,7 +2761,7 @@
       <c r="AW1" s="59"/>
     </row>
     <row r="2" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2911,7 +3035,7 @@
       <c r="AW3" s="59"/>
     </row>
     <row r="4" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3049,7 +3173,7 @@
     </row>
     <row r="5" spans="1:49" ht="15.6" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>92</v>
@@ -3185,7 +3309,7 @@
       <c r="AW5" s="59"/>
     </row>
     <row r="6" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -3322,7 +3446,7 @@
       <c r="AW6" s="59"/>
     </row>
     <row r="7" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3737,8 +3861,8 @@
       <c r="AW9" s="59"/>
     </row>
     <row r="10" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
+      <c r="A10" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>63</v>
@@ -3876,7 +4000,7 @@
       <c r="AW10" s="59"/>
     </row>
     <row r="11" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -4015,7 +4139,7 @@
       <c r="AW11" s="59"/>
     </row>
     <row r="12" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -4291,7 +4415,7 @@
       <c r="AW13" s="59"/>
     </row>
     <row r="14" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4428,8 +4552,8 @@
       <c r="AW14" s="59"/>
     </row>
     <row r="15" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
+      <c r="A15" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>39</v>
@@ -4565,8 +4689,8 @@
       <c r="AW15" s="59"/>
     </row>
     <row r="16" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>72</v>
+      <c r="A16" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>97</v>
@@ -4978,7 +5102,7 @@
       <c r="AW18" s="59"/>
     </row>
     <row r="19" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -5117,7 +5241,7 @@
       <c r="AW19" s="59"/>
     </row>
     <row r="20" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -5256,8 +5380,8 @@
       <c r="AW20" s="59"/>
     </row>
     <row r="21" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>72</v>
+      <c r="A21" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>100</v>
@@ -5394,7 +5518,7 @@
     </row>
     <row r="22" spans="1:49" ht="15.6" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>90</v>
@@ -5532,7 +5656,7 @@
       <c r="AW22" s="59"/>
     </row>
     <row r="23" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -6080,7 +6204,7 @@
       <c r="AW26" s="59"/>
     </row>
     <row r="27" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -6217,7 +6341,7 @@
       <c r="AW27" s="59"/>
     </row>
     <row r="28" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -6495,8 +6619,8 @@
       <c r="AW29" s="59"/>
     </row>
     <row r="30" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>72</v>
+      <c r="A30" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>88</v>
@@ -6632,7 +6756,7 @@
       <c r="AW30" s="59"/>
     </row>
     <row r="31" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -6772,7 +6896,7 @@
     </row>
     <row r="32" spans="1:49" ht="15.6" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>94</v>
@@ -7050,7 +7174,7 @@
     </row>
     <row r="34" spans="1:49" ht="15.6" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>46</v>
@@ -7188,7 +7312,7 @@
       <c r="AW34" s="59"/>
     </row>
     <row r="35" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -7466,7 +7590,7 @@
       <c r="AW36" s="59"/>
     </row>
     <row r="37" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -7605,7 +7729,7 @@
       <c r="AW37" s="59"/>
     </row>
     <row r="38" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B38" s="10" t="s">
@@ -7742,8 +7866,8 @@
       <c r="AW38" s="59"/>
     </row>
     <row r="39" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>72</v>
+      <c r="A39" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>81</v>
@@ -8018,7 +8142,7 @@
       <c r="AW40" s="59"/>
     </row>
     <row r="41" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -8157,7 +8281,7 @@
       <c r="AW41" s="59"/>
     </row>
     <row r="42" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -8294,7 +8418,7 @@
       <c r="AW42" s="59"/>
     </row>
     <row r="43" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -8427,7 +8551,7 @@
       <c r="AW43" s="59"/>
     </row>
     <row r="44" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -8566,7 +8690,7 @@
       <c r="AW44" s="59"/>
     </row>
     <row r="45" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -8705,7 +8829,7 @@
       <c r="AW45" s="59"/>
     </row>
     <row r="46" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -8845,7 +8969,7 @@
     </row>
     <row r="47" spans="1:49" ht="15.6" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>71</v>
@@ -8983,7 +9107,7 @@
       <c r="AW47" s="59"/>
     </row>
     <row r="48" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -9122,7 +9246,7 @@
       <c r="AW48" s="59"/>
     </row>
     <row r="49" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -9261,7 +9385,7 @@
       <c r="AW49" s="59"/>
     </row>
     <row r="50" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -9534,7 +9658,7 @@
     </row>
     <row r="52" spans="1:49" ht="15.6" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>60</v>
@@ -9672,8 +9796,8 @@
       <c r="AW52" s="59"/>
     </row>
     <row r="53" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>34</v>
+      <c r="A53" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>68</v>
@@ -9811,7 +9935,7 @@
       <c r="AW53" s="59"/>
     </row>
     <row r="54" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -9950,7 +10074,7 @@
       <c r="AW54" s="59"/>
     </row>
     <row r="55" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -10089,8 +10213,8 @@
       <c r="AW55" s="59"/>
     </row>
     <row r="56" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>34</v>
+      <c r="A56" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>66</v>
@@ -10367,7 +10491,7 @@
       <c r="AW57" s="59"/>
     </row>
     <row r="58" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -10507,7 +10631,7 @@
     </row>
     <row r="59" spans="1:49" ht="15.6" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>78</v>
@@ -10645,8 +10769,8 @@
       <c r="AW59" s="59"/>
     </row>
     <row r="60" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A60" s="2" t="s">
-        <v>34</v>
+      <c r="A60" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>41</v>
@@ -10784,7 +10908,7 @@
       <c r="AW60" s="59"/>
     </row>
     <row r="61" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B61" s="11" t="s">
@@ -10921,7 +11045,7 @@
       <c r="AW61" s="59"/>
     </row>
     <row r="62" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -11060,7 +11184,7 @@
       <c r="AW62" s="59"/>
     </row>
     <row r="63" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -11475,7 +11599,7 @@
       <c r="AW65" s="59"/>
     </row>
     <row r="66" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B66" s="10" t="s">
@@ -11612,7 +11736,7 @@
       <c r="AW66" s="59"/>
     </row>
     <row r="67" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B67" s="11" t="s">
@@ -11886,7 +12010,7 @@
       <c r="AW68" s="59"/>
     </row>
     <row r="69" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -12011,7 +12135,7 @@
       <c r="AW69" s="59"/>
     </row>
     <row r="70" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B70" s="11" t="s">
@@ -12285,7 +12409,7 @@
       <c r="AW71" s="59"/>
     </row>
     <row r="72" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B72" s="11" t="s">
@@ -12416,7 +12540,7 @@
       <c r="AW72" s="59"/>
     </row>
     <row r="73" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B73" s="7" t="s">
@@ -12555,7 +12679,7 @@
       <c r="AW73" s="59"/>
     </row>
     <row r="74" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -12825,7 +12949,7 @@
       <c r="AW75" s="59"/>
     </row>
     <row r="76" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B76" s="7" t="s">
@@ -12965,7 +13089,7 @@
     </row>
     <row r="77" spans="1:49" ht="15.6" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>54</v>
@@ -13103,7 +13227,7 @@
       <c r="AW77" s="59"/>
     </row>
     <row r="78" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -13240,7 +13364,7 @@
       <c r="AW78" s="59"/>
     </row>
     <row r="79" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B79" s="7" t="s">
@@ -13379,7 +13503,7 @@
       <c r="AW79" s="59"/>
     </row>
     <row r="80" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B80" s="10" t="s">
@@ -13656,7 +13780,7 @@
     </row>
     <row r="82" spans="1:49" ht="15.6" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>75</v>
@@ -13794,7 +13918,7 @@
       <c r="AW82" s="59"/>
     </row>
     <row r="83" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -13933,7 +14057,7 @@
       <c r="AW83" s="59"/>
     </row>
     <row r="84" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -14072,7 +14196,7 @@
       <c r="AW84" s="59"/>
     </row>
     <row r="85" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -14350,7 +14474,7 @@
       <c r="AW86" s="59"/>
     </row>
     <row r="87" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -14489,7 +14613,7 @@
       <c r="AW87" s="59"/>
     </row>
     <row r="88" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B88" s="11" t="s">
@@ -14624,7 +14748,7 @@
       <c r="AW88" s="59"/>
     </row>
     <row r="89" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B89" s="10" t="s">
@@ -14761,7 +14885,7 @@
       <c r="AW89" s="59"/>
     </row>
     <row r="90" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B90" s="11" t="s">
@@ -14892,8 +15016,8 @@
       <c r="AW90" s="59"/>
     </row>
     <row r="91" spans="1:49" ht="15.6" customHeight="1">
-      <c r="A91" s="21" t="s">
-        <v>72</v>
+      <c r="A91" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>84</v>
@@ -15030,7 +15154,7 @@
     </row>
     <row r="92" spans="1:49" ht="15.6" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>57</v>
@@ -15168,7 +15292,7 @@
       <c r="AW92" s="59"/>
     </row>
     <row r="93" spans="1:49" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B93" s="10" t="s">
@@ -15341,23 +15465,23 @@
   <sortState ref="A2:AL92">
     <sortCondition ref="B2:B92"/>
   </sortState>
-  <conditionalFormatting sqref="A79:B93">
-    <cfRule type="expression" dxfId="3" priority="7">
+  <conditionalFormatting sqref="B79:B93">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($A79&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79:C91">
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($A79&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:D91">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($A79&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL3:AO3 AL2:AN2 AL9:AO9 AL4:AN8 AP8 AL20:AO20 AL10:AN19 AL24:AO24 AL21:AN23 AL31:AO31 AL25:AN30 AP25 AL91:AO92 AL32:AN90 AP70 AL93:AN93 AP93 AP30 AQ35 AQ90 AR4 AR36:AR38 AS3 AR7 AS6 AR12:AS12 AR16:AR19 AR21 AR23 AS22 AR27:AR28 AR32 AS29 AS33:AS34 AR40:AR44 AS39 AR46:AR51 AR53:AR56 AR59:AS59 AR61:AR63 AR65:AR67 AR69 AS68 AR71:AS71 AR73:AR78 AR80:AR84 AS79 AR87:AS87 AT5 AR10:AR11 AR13:AR14 AT15 AT26 AR58 AT45 AT60 AT72 AR86 AT85 AR88:AR89 L9 L38 AT52 L90 M3 M14 M39 M65 M8 M18 M23 M25:M26 M30:M31 M35 M37 M42 M70 M79 M82 M84:M85 AT64 L64">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(L2))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15369,4 +15493,1683 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AE9053-9901-4056-AB1B-13C8BBA05697}">
+  <dimension ref="C1:I92"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C1" s="134" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1" s="135">
+        <v>10027</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I1" s="140">
+        <f>G1-D1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:9" ht="15" thickBot="1">
+      <c r="C2" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="137">
+        <v>10462</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="140">
+        <f t="shared" ref="I2:I65" si="0">G2-D2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="3:9" ht="15" thickBot="1">
+      <c r="C3" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="137">
+        <v>10541</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I3" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" ht="15" thickBot="1">
+      <c r="C4" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="137">
+        <v>10625</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" ht="15" thickBot="1">
+      <c r="C5" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="137">
+        <v>10696</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="I5" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="15" thickBot="1">
+      <c r="C6" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="137">
+        <v>10777</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" ht="15" thickBot="1">
+      <c r="C7" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="137">
+        <v>10919</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I7" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" ht="15" thickBot="1">
+      <c r="C8" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="137">
+        <v>10949</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" ht="15" thickBot="1">
+      <c r="C9" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="137">
+        <v>10951</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" ht="15" thickBot="1">
+      <c r="C10" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="137">
+        <v>11015</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="15" thickBot="1">
+      <c r="C11" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="137">
+        <v>11063</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I11" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C12" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D12" s="137">
+        <v>11103</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" ht="15" thickBot="1">
+      <c r="C13" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="137">
+        <v>11117</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I13" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" ht="15" thickBot="1">
+      <c r="C14" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="137">
+        <v>11143</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" ht="15" thickBot="1">
+      <c r="C15" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="137">
+        <v>11187</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" ht="15" thickBot="1">
+      <c r="C16" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="137">
+        <v>11340</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I16" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" ht="15" thickBot="1">
+      <c r="C17" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="137">
+        <v>11341</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" ht="15" thickBot="1">
+      <c r="C18" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="137">
+        <v>11352</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" ht="15" thickBot="1">
+      <c r="C19" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="137">
+        <v>11372</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" ht="15" thickBot="1">
+      <c r="C20" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="137">
+        <v>11373</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" ht="15" thickBot="1">
+      <c r="C21" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="137">
+        <v>11374</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" ht="15" thickBot="1">
+      <c r="C22" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D22" s="137">
+        <v>11385</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="I22" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" ht="15" thickBot="1">
+      <c r="C23" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23" s="137">
+        <v>11404</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C24" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" s="137">
+        <v>11418</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="I24" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" ht="15" thickBot="1">
+      <c r="C25" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="137">
+        <v>11422</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I25" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" ht="15" thickBot="1">
+      <c r="C26" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="138">
+        <v>11424</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C27" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D27" s="137">
+        <v>11433</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I27" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" ht="15" thickBot="1">
+      <c r="C28" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="137">
+        <v>11435</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I28" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" ht="15" thickBot="1">
+      <c r="C29" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="137">
+        <v>11437</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" ht="15" thickBot="1">
+      <c r="C30" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="137">
+        <v>11439</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I30" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" ht="15" thickBot="1">
+      <c r="C31" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="137">
+        <v>11448</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" ht="15" thickBot="1">
+      <c r="C32" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" s="137">
+        <v>11455</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I32" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" ht="15" thickBot="1">
+      <c r="C33" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D33" s="137">
+        <v>11464</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C34" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D34" s="137">
+        <v>11472</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I34" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" ht="15" thickBot="1">
+      <c r="C35" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" s="137">
+        <v>11490</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="I35" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" ht="15" thickBot="1">
+      <c r="C36" s="139" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="138">
+        <v>11495</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" ht="15" thickBot="1">
+      <c r="C37" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D37" s="137">
+        <v>11501</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I37" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" ht="15" thickBot="1">
+      <c r="C38" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="137">
+        <v>11509</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" ht="15" thickBot="1">
+      <c r="C39" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" s="137">
+        <v>11515</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" ht="15" thickBot="1">
+      <c r="C40" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="137">
+        <v>11518</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I40" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" ht="15" thickBot="1">
+      <c r="C41" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D41" s="137">
+        <v>11521</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="I41" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" ht="15" thickBot="1">
+      <c r="C42" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="137">
+        <v>11523</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I42" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" ht="15" thickBot="1">
+      <c r="C43" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" s="137">
+        <v>11525</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I43" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" ht="15" thickBot="1">
+      <c r="C44" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="137">
+        <v>11529</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I44" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9" ht="15" thickBot="1">
+      <c r="C45" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="137">
+        <v>11534</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I45" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9" ht="15" thickBot="1">
+      <c r="C46" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D46" s="137">
+        <v>11557</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I46" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" ht="15" thickBot="1">
+      <c r="C47" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="137">
+        <v>11567</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" ht="15" thickBot="1">
+      <c r="C48" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="137">
+        <v>11571</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I48" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:9" ht="15" thickBot="1">
+      <c r="C49" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D49" s="137">
+        <v>11605</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="I49" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:9" ht="15" thickBot="1">
+      <c r="C50" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="137">
+        <v>11621</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I50" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:9" ht="15" thickBot="1">
+      <c r="C51" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D51" s="137">
+        <v>11627</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:9" ht="15" thickBot="1">
+      <c r="C52" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D52" s="137">
+        <v>11639</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I52" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:9" ht="15" thickBot="1">
+      <c r="C53" s="139" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="138">
+        <v>11647</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I53" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C54" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="137">
+        <v>11658</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I54" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:9" ht="15" thickBot="1">
+      <c r="C55" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D55" s="137">
+        <v>11703</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I55" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C56" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D56" s="137">
+        <v>11708</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I56" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:9" ht="15" thickBot="1">
+      <c r="C57" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D57" s="137">
+        <v>11729</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I57" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:9" ht="15" thickBot="1">
+      <c r="C58" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="137">
+        <v>11731</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I58" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:9" ht="15" thickBot="1">
+      <c r="C59" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D59" s="137">
+        <v>11735</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I59" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:9" ht="15" thickBot="1">
+      <c r="C60" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D60" s="137">
+        <v>11759</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="I60" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:9" ht="15" thickBot="1">
+      <c r="C61" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="137">
+        <v>11760</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I61" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:9" ht="15" thickBot="1">
+      <c r="C62" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="137">
+        <v>11807</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I62" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C63" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" s="137">
+        <v>11813</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I63" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:9" ht="15" thickBot="1">
+      <c r="C64" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D64" s="137">
+        <v>11823</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I64" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:9" ht="15" thickBot="1">
+      <c r="C65" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" s="137">
+        <v>11828</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I65" s="140">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="3:9" ht="15" thickBot="1">
+      <c r="C66" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D66" s="137">
+        <v>11829</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="I66" s="140">
+        <f t="shared" ref="I66:I92" si="1">G66-D66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:9" ht="15" thickBot="1">
+      <c r="C67" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="137">
+        <v>11836</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I67" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C68" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D68" s="137">
+        <v>11839</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I68" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="3:9" ht="15" thickBot="1">
+      <c r="C69" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D69" s="137">
+        <v>11843</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="I69" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:9" ht="15" thickBot="1">
+      <c r="C70" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" s="137">
+        <v>11854</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I70" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="3:9" ht="15" thickBot="1">
+      <c r="C71" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D71" s="137">
+        <v>11855</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="I71" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:9" ht="15" thickBot="1">
+      <c r="C72" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="137">
+        <v>11861</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I72" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:9" ht="15" thickBot="1">
+      <c r="C73" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D73" s="137">
+        <v>11875</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="I73" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C74" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D74" s="137">
+        <v>11877</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="I74" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="3:9" ht="15" thickBot="1">
+      <c r="C75" s="139" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75" s="138">
+        <v>11898</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I75" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="3:9" ht="15" thickBot="1">
+      <c r="C76" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" s="137">
+        <v>11900</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I76" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="3:9" ht="15" thickBot="1">
+      <c r="C77" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D77" s="137">
+        <v>11906</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="I77" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="3:9" ht="15" thickBot="1">
+      <c r="C78" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D78" s="137">
+        <v>11974</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I78" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="3:9" ht="15" thickBot="1">
+      <c r="C79" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D79" s="137">
+        <v>11985</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I79" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="3:9" ht="15" thickBot="1">
+      <c r="C80" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D80" s="137">
+        <v>11986</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G80" s="3">
+        <v>11986</v>
+      </c>
+      <c r="I80" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="3:9" ht="15" thickBot="1">
+      <c r="C81" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D81" s="137">
+        <v>11989</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I81" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:9" ht="15" thickBot="1">
+      <c r="C82" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" s="137">
+        <v>11990</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I82" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="3:9" ht="15" thickBot="1">
+      <c r="C83" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="137">
+        <v>11996</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I83" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:9" ht="15" thickBot="1">
+      <c r="C84" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D84" s="137">
+        <v>13017</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:9" ht="15" thickBot="1">
+      <c r="C85" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D85" s="137">
+        <v>13020</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="I85" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:9" ht="15" thickBot="1">
+      <c r="C86" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" s="137">
+        <v>13058</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I86" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:9" ht="15" thickBot="1">
+      <c r="C87" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D87" s="137">
+        <v>13070</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I87" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:9" ht="15" thickBot="1">
+      <c r="C88" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D88" s="137">
+        <v>13076</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I88" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:9" ht="15" thickBot="1">
+      <c r="C89" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D89" s="137">
+        <v>13088</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="I89" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:9" ht="15" thickBot="1">
+      <c r="C90" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D90" s="137">
+        <v>13173</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G90" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I90" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="3:9" ht="27.6" thickBot="1">
+      <c r="C91" s="136" t="s">
+        <v>275</v>
+      </c>
+      <c r="D91" s="137">
+        <v>13180</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I91" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:9" ht="15" thickBot="1">
+      <c r="C92" s="136" t="s">
+        <v>317</v>
+      </c>
+      <c r="D92" s="137">
+        <v>13187</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="I92" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="C1:D92">
+    <sortCondition ref="D1:D92"/>
+  </sortState>
+  <conditionalFormatting sqref="F78:G92">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($A78&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A4D067-A2A7-4850-B265-238CCA6E5663}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1D4C6E-C6FB-49BE-9CA1-A415A2B77F8F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4311" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4311" uniqueCount="594">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1811,9 +1811,6 @@
   </si>
   <si>
     <t>Количетсво корзин с ассортиментом Кари</t>
-  </si>
-  <si>
-    <t>Нет корзин</t>
   </si>
 </sst>
 </file>
@@ -2923,39 +2920,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2974,6 +2938,39 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3384,92 +3381,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="156" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="145" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="152" t="s">
         <v>376</v>
       </c>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="145" t="s">
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="154"/>
+      <c r="Q1" s="152" t="s">
         <v>377</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="152"/>
-      <c r="W1" s="145" t="s">
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="155"/>
+      <c r="V1" s="154"/>
+      <c r="W1" s="152" t="s">
         <v>378</v>
       </c>
-      <c r="X1" s="152"/>
+      <c r="X1" s="154"/>
       <c r="Y1" s="94" t="s">
         <v>379</v>
       </c>
-      <c r="Z1" s="145" t="s">
+      <c r="Z1" s="152" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="152"/>
-      <c r="AB1" s="145" t="s">
+      <c r="AA1" s="154"/>
+      <c r="AB1" s="152" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="151"/>
-      <c r="AD1" s="152"/>
-      <c r="AE1" s="145" t="s">
+      <c r="AC1" s="161"/>
+      <c r="AD1" s="154"/>
+      <c r="AE1" s="152" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="152"/>
-      <c r="AG1" s="145" t="s">
+      <c r="AF1" s="154"/>
+      <c r="AG1" s="152" t="s">
         <v>383</v>
       </c>
-      <c r="AH1" s="146"/>
-      <c r="AI1" s="152"/>
+      <c r="AH1" s="153"/>
+      <c r="AI1" s="154"/>
       <c r="AJ1" s="119" t="s">
         <v>384</v>
       </c>
       <c r="AK1" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="AL1" s="153" t="s">
+      <c r="AL1" s="162" t="s">
         <v>386</v>
       </c>
-      <c r="AM1" s="152"/>
-      <c r="AN1" s="145" t="s">
+      <c r="AM1" s="154"/>
+      <c r="AN1" s="152" t="s">
         <v>387</v>
       </c>
-      <c r="AO1" s="146"/>
-      <c r="AP1" s="147"/>
-      <c r="AQ1" s="153" t="s">
+      <c r="AO1" s="153"/>
+      <c r="AP1" s="155"/>
+      <c r="AQ1" s="162" t="s">
         <v>584</v>
       </c>
-      <c r="AR1" s="145"/>
-      <c r="AS1" s="145"/>
-      <c r="AT1" s="145"/>
-      <c r="AU1" s="146"/>
-      <c r="AV1" s="146"/>
-      <c r="AW1" s="146"/>
-      <c r="AX1" s="152"/>
-      <c r="AY1" s="148" t="s">
+      <c r="AR1" s="152"/>
+      <c r="AS1" s="152"/>
+      <c r="AT1" s="152"/>
+      <c r="AU1" s="153"/>
+      <c r="AV1" s="153"/>
+      <c r="AW1" s="153"/>
+      <c r="AX1" s="154"/>
+      <c r="AY1" s="158" t="s">
         <v>388</v>
       </c>
-      <c r="AZ1" s="149"/>
-      <c r="BA1" s="149"/>
-      <c r="BB1" s="149"/>
-      <c r="BC1" s="149"/>
-      <c r="BD1" s="150"/>
+      <c r="AZ1" s="159"/>
+      <c r="BA1" s="159"/>
+      <c r="BB1" s="159"/>
+      <c r="BC1" s="159"/>
+      <c r="BD1" s="160"/>
       <c r="BE1" s="21"/>
     </row>
     <row r="2" spans="1:57" ht="61.8" thickBot="1">
@@ -3599,7 +3596,7 @@
       <c r="AP2" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="AQ2" s="162" t="s">
+      <c r="AQ2" s="151" t="s">
         <v>25</v>
       </c>
       <c r="AR2" s="84" t="s">
@@ -3775,10 +3772,10 @@
         <v>4</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU3" s="2">
         <v>7</v>
@@ -3938,16 +3935,16 @@
         <v>135</v>
       </c>
       <c r="AQ4" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR4" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS4" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT4" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU4" s="2">
         <v>2</v>
@@ -4107,16 +4104,16 @@
         <v>135</v>
       </c>
       <c r="AQ5" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR5" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS5" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT5" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU5" s="2">
         <v>2</v>
@@ -4282,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="AS6" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT6" s="2">
         <v>8</v>
@@ -4451,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="AS7" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT7" s="2">
         <v>6</v>
@@ -4620,7 +4617,7 @@
         <v>4</v>
       </c>
       <c r="AS8" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT8" s="2">
         <v>6</v>
@@ -4789,7 +4786,7 @@
         <v>2</v>
       </c>
       <c r="AS9" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT9" s="2">
         <v>2</v>
@@ -4952,16 +4949,16 @@
         <v>130</v>
       </c>
       <c r="AQ10" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS10" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU10" s="2">
         <v>5</v>
@@ -5127,7 +5124,7 @@
         <v>3</v>
       </c>
       <c r="AS11" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT11" s="2">
         <v>8</v>
@@ -5290,16 +5287,16 @@
         <v>135</v>
       </c>
       <c r="AQ12" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS12" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT12" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU12" s="2">
         <v>2</v>
@@ -5457,16 +5454,16 @@
         <v>135</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR13" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS13" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT13" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU13" s="2">
         <v>16</v>
@@ -5626,16 +5623,16 @@
         <v>130</v>
       </c>
       <c r="AQ14" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS14" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT14" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU14" s="2">
         <v>5</v>
@@ -5795,16 +5792,16 @@
         <v>135</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR15" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS15" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT15" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU15" s="2">
         <v>4</v>
@@ -5964,16 +5961,16 @@
         <v>135</v>
       </c>
       <c r="AQ16" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR16" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS16" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT16" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU16" s="2">
         <v>5</v>
@@ -6133,16 +6130,16 @@
         <v>135</v>
       </c>
       <c r="AQ17" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR17" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS17" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT17" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU17" s="2">
         <v>4</v>
@@ -6302,16 +6299,16 @@
         <v>135</v>
       </c>
       <c r="AQ18" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR18" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS18" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT18" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU18" s="2">
         <v>5</v>
@@ -6471,16 +6468,16 @@
         <v>135</v>
       </c>
       <c r="AQ19" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS19" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT19" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU19" s="2" t="s">
         <v>27</v>
@@ -6640,16 +6637,16 @@
         <v>135</v>
       </c>
       <c r="AQ20" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS20" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT20" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU20" s="2">
         <v>10</v>
@@ -6815,7 +6812,7 @@
         <v>2</v>
       </c>
       <c r="AS21" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT21" s="2">
         <v>2</v>
@@ -6978,16 +6975,16 @@
         <v>135</v>
       </c>
       <c r="AQ22" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR22" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS22" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT22" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU22" s="2">
         <v>5</v>
@@ -7147,16 +7144,16 @@
         <v>135</v>
       </c>
       <c r="AQ23" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR23" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS23" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT23" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU23" s="2">
         <v>5</v>
@@ -7478,16 +7475,16 @@
         <v>206</v>
       </c>
       <c r="AQ25" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR25" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS25" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT25" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU25" s="2">
         <v>3</v>
@@ -7650,13 +7647,13 @@
         <v>3</v>
       </c>
       <c r="AR26" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS26" s="2">
         <v>1</v>
       </c>
       <c r="AT26" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU26" s="2">
         <v>10</v>
@@ -7816,16 +7813,16 @@
         <v>138</v>
       </c>
       <c r="AQ27" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR27" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS27" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT27" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU27" s="2">
         <v>12</v>
@@ -7985,16 +7982,16 @@
         <v>135</v>
       </c>
       <c r="AQ28" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR28" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS28" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT28" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU28" s="2">
         <v>3</v>
@@ -8154,16 +8151,16 @@
         <v>297</v>
       </c>
       <c r="AQ29" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR29" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS29" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT29" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU29" s="2">
         <v>8</v>
@@ -8323,16 +8320,16 @@
         <v>135</v>
       </c>
       <c r="AQ30" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR30" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS30" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT30" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU30" s="2" t="s">
         <v>27</v>
@@ -8495,7 +8492,7 @@
         <v>7</v>
       </c>
       <c r="AR31" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS31" s="2">
         <v>6</v>
@@ -8667,7 +8664,7 @@
         <v>2</v>
       </c>
       <c r="AS32" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT32" s="2">
         <v>2</v>
@@ -8830,16 +8827,16 @@
         <v>202</v>
       </c>
       <c r="AQ33" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR33" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS33" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT33" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU33" s="2">
         <v>4</v>
@@ -8999,16 +8996,16 @@
         <v>135</v>
       </c>
       <c r="AQ34" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR34" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS34" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT34" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU34" s="2">
         <v>3</v>
@@ -9171,10 +9168,10 @@
         <v>4</v>
       </c>
       <c r="AR35" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS35" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT35" s="2">
         <v>4</v>
@@ -9337,16 +9334,16 @@
         <v>135</v>
       </c>
       <c r="AQ36" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR36" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS36" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT36" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU36" s="2">
         <v>7</v>
@@ -9506,16 +9503,16 @@
         <v>170</v>
       </c>
       <c r="AQ37" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR37" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS37" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT37" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU37" s="2">
         <v>7</v>
@@ -9675,16 +9672,16 @@
         <v>135</v>
       </c>
       <c r="AQ38" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR38" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS38" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT38" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU38" s="2">
         <v>5</v>
@@ -9845,7 +9842,7 @@
         <v>4</v>
       </c>
       <c r="AR39" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS39" s="2">
         <v>2</v>
@@ -10011,16 +10008,16 @@
         <v>135</v>
       </c>
       <c r="AQ40" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR40" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS40" s="2">
         <v>2</v>
       </c>
       <c r="AT40" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU40" s="2">
         <v>4</v>
@@ -10180,7 +10177,7 @@
         <v>135</v>
       </c>
       <c r="AQ41" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR41" s="2">
         <v>10</v>
@@ -10189,7 +10186,7 @@
         <v>10</v>
       </c>
       <c r="AT41" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU41" s="2">
         <v>2</v>
@@ -10349,16 +10346,16 @@
         <v>138</v>
       </c>
       <c r="AQ42" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR42" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS42" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT42" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU42" s="2">
         <v>4</v>
@@ -10516,16 +10513,16 @@
         <v>138</v>
       </c>
       <c r="AQ43" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR43" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS43" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT43" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU43" s="2">
         <v>4</v>
@@ -10683,10 +10680,10 @@
         <v>6</v>
       </c>
       <c r="AR44" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS44" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT44" s="2">
         <v>6</v>
@@ -10849,16 +10846,16 @@
         <v>135</v>
       </c>
       <c r="AQ45" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR45" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS45" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT45" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU45" s="2">
         <v>2</v>
@@ -11018,16 +11015,16 @@
         <v>164</v>
       </c>
       <c r="AQ46" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR46" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS46" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT46" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU46" s="2">
         <v>4</v>
@@ -11187,16 +11184,16 @@
         <v>135</v>
       </c>
       <c r="AQ47" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR47" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS47" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT47" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU47" s="2">
         <v>4</v>
@@ -11356,16 +11353,16 @@
         <v>135</v>
       </c>
       <c r="AQ48" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR48" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS48" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT48" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU48" s="2">
         <v>5</v>
@@ -11531,7 +11528,7 @@
         <v>4</v>
       </c>
       <c r="AS49" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT49" s="2">
         <v>4</v>
@@ -11694,16 +11691,16 @@
         <v>135</v>
       </c>
       <c r="AQ50" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR50" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS50" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT50" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU50" s="2">
         <v>3</v>
@@ -11861,16 +11858,16 @@
         <v>135</v>
       </c>
       <c r="AQ51" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR51" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS51" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT51" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU51" s="2">
         <v>2</v>
@@ -12030,16 +12027,16 @@
         <v>130</v>
       </c>
       <c r="AQ52" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR52" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS52" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT52" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU52" s="2">
         <v>3</v>
@@ -12199,16 +12196,16 @@
         <v>170</v>
       </c>
       <c r="AQ53" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR53" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS53" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT53" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU53" s="2">
         <v>3</v>
@@ -12374,10 +12371,10 @@
         <v>4</v>
       </c>
       <c r="AS54" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT54" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU54" s="2">
         <v>2</v>
@@ -12537,16 +12534,16 @@
         <v>135</v>
       </c>
       <c r="AQ55" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR55" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS55" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT55" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU55" s="2">
         <v>10</v>
@@ -12706,16 +12703,16 @@
         <v>130</v>
       </c>
       <c r="AQ56" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR56" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS56" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT56" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU56" s="2">
         <v>2</v>
@@ -12878,13 +12875,13 @@
         <v>2</v>
       </c>
       <c r="AR57" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS57" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT57" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU57" s="2">
         <v>5</v>
@@ -13044,16 +13041,16 @@
         <v>286</v>
       </c>
       <c r="AQ58" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR58" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS58" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT58" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU58" s="2" t="s">
         <v>27</v>
@@ -13219,7 +13216,7 @@
         <v>2</v>
       </c>
       <c r="AS59" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT59" s="2">
         <v>2</v>
@@ -13385,10 +13382,10 @@
         <v>6</v>
       </c>
       <c r="AR60" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS60" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT60" s="2">
         <v>6</v>
@@ -13551,16 +13548,16 @@
         <v>135</v>
       </c>
       <c r="AQ61" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR61" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS61" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT61" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU61" s="2">
         <v>4</v>
@@ -13724,7 +13721,7 @@
         <v>8</v>
       </c>
       <c r="AS62" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT62" s="2">
         <v>8</v>
@@ -14056,16 +14053,16 @@
         <v>170</v>
       </c>
       <c r="AQ64" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR64" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS64" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT64" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU64" s="2">
         <v>8</v>
@@ -14225,16 +14222,16 @@
         <v>135</v>
       </c>
       <c r="AQ65" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR65" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS65" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT65" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU65" s="2">
         <v>8</v>
@@ -14561,16 +14558,16 @@
         <v>135</v>
       </c>
       <c r="AQ67" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR67" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS67" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT67" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU67" s="2">
         <v>1</v>
@@ -14734,7 +14731,7 @@
         <v>20</v>
       </c>
       <c r="AS68" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT68" s="2">
         <v>20</v>
@@ -14897,16 +14894,16 @@
         <v>135</v>
       </c>
       <c r="AQ69" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR69" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS69" s="2">
         <v>1</v>
       </c>
       <c r="AT69" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU69" s="2">
         <v>2</v>
@@ -15061,16 +15058,16 @@
       </c>
       <c r="AP70" s="122"/>
       <c r="AQ70" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR70" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS70" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT70" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU70" s="2">
         <v>2</v>
@@ -15228,16 +15225,16 @@
         <v>347</v>
       </c>
       <c r="AQ71" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR71" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS71" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT71" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU71" s="2">
         <v>4</v>
@@ -15406,7 +15403,7 @@
         <v>4</v>
       </c>
       <c r="AT72" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU72" s="2">
         <v>5</v>
@@ -15559,16 +15556,16 @@
       </c>
       <c r="AP73" s="122"/>
       <c r="AQ73" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR73" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS73" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT73" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU73" s="2">
         <v>4</v>
@@ -15728,16 +15725,16 @@
         <v>135</v>
       </c>
       <c r="AQ74" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR74" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS74" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT74" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU74" s="2">
         <v>2</v>
@@ -15896,10 +15893,10 @@
         <v>6</v>
       </c>
       <c r="AS75" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT75" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU75" s="2">
         <v>3</v>
@@ -16059,16 +16056,16 @@
         <v>138</v>
       </c>
       <c r="AQ76" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR76" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS76" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT76" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU76" s="2">
         <v>2</v>
@@ -16228,16 +16225,16 @@
         <v>138</v>
       </c>
       <c r="AQ77" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR77" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS77" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT77" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU77" s="2">
         <v>3</v>
@@ -16400,13 +16397,13 @@
         <v>6</v>
       </c>
       <c r="AR78" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS78" s="2">
         <v>6</v>
       </c>
       <c r="AT78" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU78" s="2">
         <v>4</v>
@@ -16564,16 +16561,16 @@
         <v>135</v>
       </c>
       <c r="AQ79" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR79" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS79" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT79" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU79" s="2">
         <v>1</v>
@@ -16733,7 +16730,7 @@
         <v>138</v>
       </c>
       <c r="AQ80" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR80" s="2">
         <v>4</v>
@@ -16742,7 +16739,7 @@
         <v>4</v>
       </c>
       <c r="AT80" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU80" s="2">
         <v>5</v>
@@ -16900,16 +16897,16 @@
         <v>138</v>
       </c>
       <c r="AQ81" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR81" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS81" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT81" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU81" s="2">
         <v>2</v>
@@ -17069,16 +17066,16 @@
         <v>135</v>
       </c>
       <c r="AQ82" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR82" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS82" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT82" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU82" s="2">
         <v>2</v>
@@ -17407,16 +17404,16 @@
         <v>135</v>
       </c>
       <c r="AQ84" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR84" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS84" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT84" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU84" s="2">
         <v>5</v>
@@ -17582,7 +17579,7 @@
         <v>5</v>
       </c>
       <c r="AS85" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT85" s="2">
         <v>5</v>
@@ -17745,10 +17742,10 @@
         <v>214</v>
       </c>
       <c r="AQ86" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR86" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS86" s="2">
         <v>6</v>
@@ -17914,16 +17911,16 @@
         <v>240</v>
       </c>
       <c r="AQ87" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR87" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS87" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT87" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU87" s="2">
         <v>4</v>
@@ -18083,16 +18080,16 @@
         <v>0</v>
       </c>
       <c r="AQ88" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR88" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS88" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT88" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU88" s="2">
         <v>2</v>
@@ -18256,7 +18253,7 @@
         <v>20</v>
       </c>
       <c r="AS89" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT89" s="2">
         <v>20</v>
@@ -18417,16 +18414,16 @@
         <v>138</v>
       </c>
       <c r="AQ90" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR90" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS90" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT90" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU90" s="2">
         <v>2</v>
@@ -18579,16 +18576,16 @@
       </c>
       <c r="AP91" s="122"/>
       <c r="AQ91" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR91" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS91" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT91" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU91" s="2">
         <v>18</v>
@@ -18748,16 +18745,16 @@
         <v>135</v>
       </c>
       <c r="AQ92" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR92" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS92" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT92" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU92" s="2">
         <v>3</v>
@@ -18917,16 +18914,16 @@
         <v>170</v>
       </c>
       <c r="AQ93" s="10" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR93" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS93" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT93" s="2" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU93" s="2">
         <v>7</v>
@@ -19080,16 +19077,16 @@
       <c r="AO94" s="39"/>
       <c r="AP94" s="144"/>
       <c r="AQ94" s="15" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AR94" s="17" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AS94" s="17" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AT94" s="17" t="s">
-        <v>594</v>
+        <v>27</v>
       </c>
       <c r="AU94" s="17">
         <v>7</v>
@@ -19187,11 +19184,6 @@
     <sortCondition ref="C3:C93"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="AN1:AP1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -19199,6 +19191,11 @@
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AQ1:AX1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C80:C94">
     <cfRule type="expression" dxfId="11" priority="14">
@@ -19282,13 +19279,13 @@
       <c r="C2" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="156" t="s">
+      <c r="E2" s="145" t="s">
         <v>266</v>
       </c>
-      <c r="F2" s="157">
+      <c r="F2" s="146">
         <v>10027</v>
       </c>
-      <c r="H2" s="161">
+      <c r="H2" s="150">
         <f>F2-C2</f>
         <v>0</v>
       </c>
@@ -19300,13 +19297,13 @@
       <c r="C3" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="158" t="s">
+      <c r="E3" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F3" s="159">
+      <c r="F3" s="148">
         <v>10462</v>
       </c>
-      <c r="H3" s="161">
+      <c r="H3" s="150">
         <f t="shared" ref="H3:H66" si="0">F3-C3</f>
         <v>0</v>
       </c>
@@ -19318,13 +19315,13 @@
       <c r="C4" s="64" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="159">
+      <c r="F4" s="148">
         <v>10541</v>
       </c>
-      <c r="H4" s="161">
+      <c r="H4" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19336,13 +19333,13 @@
       <c r="C5" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="158" t="s">
+      <c r="E5" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="159">
+      <c r="F5" s="148">
         <v>10625</v>
       </c>
-      <c r="H5" s="161">
+      <c r="H5" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19354,13 +19351,13 @@
       <c r="C6" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="E6" s="158" t="s">
+      <c r="E6" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="159">
+      <c r="F6" s="148">
         <v>10696</v>
       </c>
-      <c r="H6" s="161">
+      <c r="H6" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19372,13 +19369,13 @@
       <c r="C7" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="158" t="s">
+      <c r="E7" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="159">
+      <c r="F7" s="148">
         <v>10777</v>
       </c>
-      <c r="H7" s="161">
+      <c r="H7" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19390,13 +19387,13 @@
       <c r="C8" s="64" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="158" t="s">
+      <c r="E8" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F8" s="159">
+      <c r="F8" s="148">
         <v>10919</v>
       </c>
-      <c r="H8" s="161">
+      <c r="H8" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19408,13 +19405,13 @@
       <c r="C9" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="158" t="s">
+      <c r="E9" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="159">
+      <c r="F9" s="148">
         <v>10949</v>
       </c>
-      <c r="H9" s="161">
+      <c r="H9" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19426,13 +19423,13 @@
       <c r="C10" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="158" t="s">
+      <c r="E10" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F10" s="159">
+      <c r="F10" s="148">
         <v>10951</v>
       </c>
-      <c r="H10" s="161">
+      <c r="H10" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19444,13 +19441,13 @@
       <c r="C11" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="158" t="s">
+      <c r="E11" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="159">
+      <c r="F11" s="148">
         <v>11015</v>
       </c>
-      <c r="H11" s="161">
+      <c r="H11" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19462,13 +19459,13 @@
       <c r="C12" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="158" t="s">
+      <c r="E12" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F12" s="160">
+      <c r="F12" s="149">
         <v>11063</v>
       </c>
-      <c r="H12" s="161">
+      <c r="H12" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19480,13 +19477,13 @@
       <c r="C13" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="E13" s="158" t="s">
+      <c r="E13" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F13" s="159">
+      <c r="F13" s="148">
         <v>11103</v>
       </c>
-      <c r="H13" s="161">
+      <c r="H13" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19498,13 +19495,13 @@
       <c r="C14" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="E14" s="158" t="s">
+      <c r="E14" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F14" s="159">
+      <c r="F14" s="148">
         <v>11117</v>
       </c>
-      <c r="H14" s="161">
+      <c r="H14" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19516,13 +19513,13 @@
       <c r="C15" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="158" t="s">
+      <c r="E15" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F15" s="159">
+      <c r="F15" s="148">
         <v>11143</v>
       </c>
-      <c r="H15" s="161">
+      <c r="H15" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19534,13 +19531,13 @@
       <c r="C16" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="158" t="s">
+      <c r="E16" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="159">
+      <c r="F16" s="148">
         <v>11187</v>
       </c>
-      <c r="H16" s="161">
+      <c r="H16" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19552,13 +19549,13 @@
       <c r="C17" s="64" t="s">
         <v>261</v>
       </c>
-      <c r="E17" s="158" t="s">
+      <c r="E17" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="159">
+      <c r="F17" s="148">
         <v>11340</v>
       </c>
-      <c r="H17" s="161">
+      <c r="H17" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19570,13 +19567,13 @@
       <c r="C18" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="E18" s="158" t="s">
+      <c r="E18" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="159">
+      <c r="F18" s="148">
         <v>11341</v>
       </c>
-      <c r="H18" s="161">
+      <c r="H18" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19588,13 +19585,13 @@
       <c r="C19" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="E19" s="158" t="s">
+      <c r="E19" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F19" s="159">
+      <c r="F19" s="148">
         <v>11352</v>
       </c>
-      <c r="H19" s="161">
+      <c r="H19" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19606,13 +19603,13 @@
       <c r="C20" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="E20" s="158" t="s">
+      <c r="E20" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="159">
+      <c r="F20" s="148">
         <v>11372</v>
       </c>
-      <c r="H20" s="161">
+      <c r="H20" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19624,13 +19621,13 @@
       <c r="C21" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="158" t="s">
+      <c r="E21" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="159">
+      <c r="F21" s="148">
         <v>11373</v>
       </c>
-      <c r="H21" s="161">
+      <c r="H21" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19642,13 +19639,13 @@
       <c r="C22" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="158" t="s">
+      <c r="E22" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="159">
+      <c r="F22" s="148">
         <v>11374</v>
       </c>
-      <c r="H22" s="161">
+      <c r="H22" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19660,13 +19657,13 @@
       <c r="C23" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="E23" s="158" t="s">
+      <c r="E23" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F23" s="160">
+      <c r="F23" s="149">
         <v>11385</v>
       </c>
-      <c r="H23" s="161">
+      <c r="H23" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19678,13 +19675,13 @@
       <c r="C24" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="158" t="s">
+      <c r="E24" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F24" s="159">
+      <c r="F24" s="148">
         <v>11404</v>
       </c>
-      <c r="H24" s="161">
+      <c r="H24" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19696,13 +19693,13 @@
       <c r="C25" s="64" t="s">
         <v>291</v>
       </c>
-      <c r="E25" s="158" t="s">
+      <c r="E25" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F25" s="159">
+      <c r="F25" s="148">
         <v>11418</v>
       </c>
-      <c r="H25" s="161">
+      <c r="H25" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19714,13 +19711,13 @@
       <c r="C26" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="E26" s="158" t="s">
+      <c r="E26" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F26" s="159">
+      <c r="F26" s="148">
         <v>11422</v>
       </c>
-      <c r="H26" s="161">
+      <c r="H26" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19732,13 +19729,13 @@
       <c r="C27" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="E27" s="158" t="s">
+      <c r="E27" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="159">
+      <c r="F27" s="148">
         <v>11424</v>
       </c>
-      <c r="H27" s="161">
+      <c r="H27" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19750,13 +19747,13 @@
       <c r="C28" s="64" t="s">
         <v>296</v>
       </c>
-      <c r="E28" s="158" t="s">
+      <c r="E28" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F28" s="159">
+      <c r="F28" s="148">
         <v>11433</v>
       </c>
-      <c r="H28" s="161">
+      <c r="H28" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19768,13 +19765,13 @@
       <c r="C29" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="E29" s="158" t="s">
+      <c r="E29" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="159">
+      <c r="F29" s="148">
         <v>11435</v>
       </c>
-      <c r="H29" s="161">
+      <c r="H29" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19786,13 +19783,13 @@
       <c r="C30" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="158" t="s">
+      <c r="E30" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="159">
+      <c r="F30" s="148">
         <v>11437</v>
       </c>
-      <c r="H30" s="161">
+      <c r="H30" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19804,13 +19801,13 @@
       <c r="C31" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="E31" s="158" t="s">
+      <c r="E31" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="159">
+      <c r="F31" s="148">
         <v>11439</v>
       </c>
-      <c r="H31" s="161">
+      <c r="H31" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19822,13 +19819,13 @@
       <c r="C32" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="E32" s="158" t="s">
+      <c r="E32" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F32" s="159">
+      <c r="F32" s="148">
         <v>11448</v>
       </c>
-      <c r="H32" s="161">
+      <c r="H32" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19840,13 +19837,13 @@
       <c r="C33" s="64" t="s">
         <v>246</v>
       </c>
-      <c r="E33" s="158" t="s">
+      <c r="E33" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F33" s="159">
+      <c r="F33" s="148">
         <v>11455</v>
       </c>
-      <c r="H33" s="161">
+      <c r="H33" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19858,13 +19855,13 @@
       <c r="C34" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="158" t="s">
+      <c r="E34" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F34" s="159">
+      <c r="F34" s="148">
         <v>11464</v>
       </c>
-      <c r="H34" s="161">
+      <c r="H34" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19876,13 +19873,13 @@
       <c r="C35" s="64" t="s">
         <v>294</v>
       </c>
-      <c r="E35" s="158" t="s">
+      <c r="E35" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F35" s="159">
+      <c r="F35" s="148">
         <v>11472</v>
       </c>
-      <c r="H35" s="161">
+      <c r="H35" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19894,13 +19891,13 @@
       <c r="C36" s="64" t="s">
         <v>264</v>
       </c>
-      <c r="E36" s="158" t="s">
+      <c r="E36" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F36" s="159">
+      <c r="F36" s="148">
         <v>11490</v>
       </c>
-      <c r="H36" s="161">
+      <c r="H36" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19912,13 +19909,13 @@
       <c r="C37" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="158" t="s">
+      <c r="E37" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="159">
+      <c r="F37" s="148">
         <v>11495</v>
       </c>
-      <c r="H37" s="161">
+      <c r="H37" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19930,13 +19927,13 @@
       <c r="C38" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="E38" s="158" t="s">
+      <c r="E38" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F38" s="160">
+      <c r="F38" s="149">
         <v>11501</v>
       </c>
-      <c r="H38" s="161">
+      <c r="H38" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19948,13 +19945,13 @@
       <c r="C39" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="E39" s="158" t="s">
+      <c r="E39" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="159">
+      <c r="F39" s="148">
         <v>11509</v>
       </c>
-      <c r="H39" s="161">
+      <c r="H39" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19966,13 +19963,13 @@
       <c r="C40" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="158" t="s">
+      <c r="E40" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F40" s="159">
+      <c r="F40" s="148">
         <v>11515</v>
       </c>
-      <c r="H40" s="161">
+      <c r="H40" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19984,13 +19981,13 @@
       <c r="C41" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="E41" s="158" t="s">
+      <c r="E41" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F41" s="159">
+      <c r="F41" s="148">
         <v>11518</v>
       </c>
-      <c r="H41" s="161">
+      <c r="H41" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20002,13 +19999,13 @@
       <c r="C42" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="E42" s="158" t="s">
+      <c r="E42" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F42" s="160">
+      <c r="F42" s="149">
         <v>11521</v>
       </c>
-      <c r="H42" s="161">
+      <c r="H42" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20020,13 +20017,13 @@
       <c r="C43" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="158" t="s">
+      <c r="E43" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F43" s="159">
+      <c r="F43" s="148">
         <v>11523</v>
       </c>
-      <c r="H43" s="161">
+      <c r="H43" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20038,13 +20035,13 @@
       <c r="C44" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="E44" s="158" t="s">
+      <c r="E44" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F44" s="159">
+      <c r="F44" s="148">
         <v>11525</v>
       </c>
-      <c r="H44" s="161">
+      <c r="H44" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20056,13 +20053,13 @@
       <c r="C45" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="158" t="s">
+      <c r="E45" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="159">
+      <c r="F45" s="148">
         <v>11529</v>
       </c>
-      <c r="H45" s="161">
+      <c r="H45" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20074,13 +20071,13 @@
       <c r="C46" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="E46" s="158" t="s">
+      <c r="E46" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F46" s="159">
+      <c r="F46" s="148">
         <v>11534</v>
       </c>
-      <c r="H46" s="161">
+      <c r="H46" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20092,13 +20089,13 @@
       <c r="C47" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="158" t="s">
+      <c r="E47" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F47" s="159">
+      <c r="F47" s="148">
         <v>11557</v>
       </c>
-      <c r="H47" s="161">
+      <c r="H47" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20110,13 +20107,13 @@
       <c r="C48" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="158" t="s">
+      <c r="E48" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="159">
+      <c r="F48" s="148">
         <v>11567</v>
       </c>
-      <c r="H48" s="161">
+      <c r="H48" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20128,13 +20125,13 @@
       <c r="C49" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="E49" s="158" t="s">
+      <c r="E49" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F49" s="159">
+      <c r="F49" s="148">
         <v>11571</v>
       </c>
-      <c r="H49" s="161">
+      <c r="H49" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20146,13 +20143,13 @@
       <c r="C50" s="67" t="s">
         <v>325</v>
       </c>
-      <c r="E50" s="158" t="s">
+      <c r="E50" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F50" s="160">
+      <c r="F50" s="149">
         <v>11605</v>
       </c>
-      <c r="H50" s="161">
+      <c r="H50" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20164,13 +20161,13 @@
       <c r="C51" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="E51" s="158" t="s">
+      <c r="E51" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F51" s="159">
+      <c r="F51" s="148">
         <v>11621</v>
       </c>
-      <c r="H51" s="161">
+      <c r="H51" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20182,13 +20179,13 @@
       <c r="C52" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="158" t="s">
+      <c r="E52" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F52" s="159">
+      <c r="F52" s="148">
         <v>11627</v>
       </c>
-      <c r="H52" s="161">
+      <c r="H52" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20200,13 +20197,13 @@
       <c r="C53" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="E53" s="158" t="s">
+      <c r="E53" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F53" s="159">
+      <c r="F53" s="148">
         <v>11639</v>
       </c>
-      <c r="H53" s="161">
+      <c r="H53" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20218,13 +20215,13 @@
       <c r="C54" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="E54" s="158" t="s">
+      <c r="E54" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F54" s="159">
+      <c r="F54" s="148">
         <v>11647</v>
       </c>
-      <c r="H54" s="161">
+      <c r="H54" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20236,13 +20233,13 @@
       <c r="C55" s="64" t="s">
         <v>278</v>
       </c>
-      <c r="E55" s="158" t="s">
+      <c r="E55" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F55" s="159">
+      <c r="F55" s="148">
         <v>11658</v>
       </c>
-      <c r="H55" s="161">
+      <c r="H55" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20254,13 +20251,13 @@
       <c r="C56" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="E56" s="158" t="s">
+      <c r="E56" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F56" s="159">
+      <c r="F56" s="148">
         <v>11703</v>
       </c>
-      <c r="H56" s="161">
+      <c r="H56" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20272,13 +20269,13 @@
       <c r="C57" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="E57" s="158" t="s">
+      <c r="E57" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F57" s="159">
+      <c r="F57" s="148">
         <v>11708</v>
       </c>
-      <c r="H57" s="161">
+      <c r="H57" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20290,13 +20287,13 @@
       <c r="C58" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="E58" s="158" t="s">
+      <c r="E58" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F58" s="159">
+      <c r="F58" s="148">
         <v>11729</v>
       </c>
-      <c r="H58" s="161">
+      <c r="H58" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20308,13 +20305,13 @@
       <c r="C59" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E59" s="158" t="s">
+      <c r="E59" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F59" s="159">
+      <c r="F59" s="148">
         <v>11731</v>
       </c>
-      <c r="H59" s="161">
+      <c r="H59" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20326,13 +20323,13 @@
       <c r="C60" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="E60" s="158" t="s">
+      <c r="E60" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F60" s="159">
+      <c r="F60" s="148">
         <v>11735</v>
       </c>
-      <c r="H60" s="161">
+      <c r="H60" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20344,13 +20341,13 @@
       <c r="C61" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="E61" s="158" t="s">
+      <c r="E61" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F61" s="160">
+      <c r="F61" s="149">
         <v>11759</v>
       </c>
-      <c r="H61" s="161">
+      <c r="H61" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20362,13 +20359,13 @@
       <c r="C62" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="E62" s="158" t="s">
+      <c r="E62" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F62" s="159">
+      <c r="F62" s="148">
         <v>11760</v>
       </c>
-      <c r="H62" s="161">
+      <c r="H62" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20380,13 +20377,13 @@
       <c r="C63" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="E63" s="158" t="s">
+      <c r="E63" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F63" s="159">
+      <c r="F63" s="148">
         <v>11807</v>
       </c>
-      <c r="H63" s="161">
+      <c r="H63" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20398,13 +20395,13 @@
       <c r="C64" s="64" t="s">
         <v>273</v>
       </c>
-      <c r="E64" s="158" t="s">
+      <c r="E64" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F64" s="159">
+      <c r="F64" s="148">
         <v>11813</v>
       </c>
-      <c r="H64" s="161">
+      <c r="H64" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20416,13 +20413,13 @@
       <c r="C65" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="158" t="s">
+      <c r="E65" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="159">
+      <c r="F65" s="148">
         <v>11823</v>
       </c>
-      <c r="H65" s="161">
+      <c r="H65" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20434,13 +20431,13 @@
       <c r="C66" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="E66" s="158" t="s">
+      <c r="E66" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F66" s="160">
+      <c r="F66" s="149">
         <v>11828</v>
       </c>
-      <c r="H66" s="161">
+      <c r="H66" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20452,13 +20449,13 @@
       <c r="C67" s="67" t="s">
         <v>268</v>
       </c>
-      <c r="E67" s="158" t="s">
+      <c r="E67" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F67" s="160">
+      <c r="F67" s="149">
         <v>11829</v>
       </c>
-      <c r="H67" s="161">
+      <c r="H67" s="150">
         <f t="shared" ref="H67:H93" si="1">F67-C67</f>
         <v>0</v>
       </c>
@@ -20470,13 +20467,13 @@
       <c r="C68" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="E68" s="158" t="s">
+      <c r="E68" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F68" s="159">
+      <c r="F68" s="148">
         <v>11836</v>
       </c>
-      <c r="H68" s="161">
+      <c r="H68" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20488,13 +20485,13 @@
       <c r="C69" s="64" t="s">
         <v>283</v>
       </c>
-      <c r="E69" s="158" t="s">
+      <c r="E69" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F69" s="159">
+      <c r="F69" s="148">
         <v>11839</v>
       </c>
-      <c r="H69" s="161">
+      <c r="H69" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20506,13 +20503,13 @@
       <c r="C70" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="E70" s="158" t="s">
+      <c r="E70" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F70" s="160">
+      <c r="F70" s="149">
         <v>11843</v>
       </c>
-      <c r="H70" s="161">
+      <c r="H70" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20524,13 +20521,13 @@
       <c r="C71" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="E71" s="158" t="s">
+      <c r="E71" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F71" s="159">
+      <c r="F71" s="148">
         <v>11854</v>
       </c>
-      <c r="H71" s="161">
+      <c r="H71" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20542,13 +20539,13 @@
       <c r="C72" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="E72" s="158" t="s">
+      <c r="E72" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F72" s="160">
+      <c r="F72" s="149">
         <v>11855</v>
       </c>
-      <c r="H72" s="161">
+      <c r="H72" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20560,13 +20557,13 @@
       <c r="C73" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="E73" s="158" t="s">
+      <c r="E73" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F73" s="159">
+      <c r="F73" s="148">
         <v>11861</v>
       </c>
-      <c r="H73" s="161">
+      <c r="H73" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20578,13 +20575,13 @@
       <c r="C74" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="E74" s="158" t="s">
+      <c r="E74" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F74" s="160">
+      <c r="F74" s="149">
         <v>11875</v>
       </c>
-      <c r="H74" s="161">
+      <c r="H74" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20596,13 +20593,13 @@
       <c r="C75" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="E75" s="158" t="s">
+      <c r="E75" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F75" s="159">
+      <c r="F75" s="148">
         <v>11877</v>
       </c>
-      <c r="H75" s="161">
+      <c r="H75" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20614,13 +20611,13 @@
       <c r="C76" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="E76" s="158" t="s">
+      <c r="E76" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F76" s="159">
+      <c r="F76" s="148">
         <v>11898</v>
       </c>
-      <c r="H76" s="161">
+      <c r="H76" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20632,13 +20629,13 @@
       <c r="C77" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E77" s="158" t="s">
+      <c r="E77" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="159">
+      <c r="F77" s="148">
         <v>11900</v>
       </c>
-      <c r="H77" s="161">
+      <c r="H77" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20650,13 +20647,13 @@
       <c r="C78" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="E78" s="158" t="s">
+      <c r="E78" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F78" s="160">
+      <c r="F78" s="149">
         <v>11906</v>
       </c>
-      <c r="H78" s="161">
+      <c r="H78" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20668,13 +20665,13 @@
       <c r="C79" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="E79" s="158" t="s">
+      <c r="E79" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F79" s="159">
+      <c r="F79" s="148">
         <v>11974</v>
       </c>
-      <c r="H79" s="161">
+      <c r="H79" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20686,13 +20683,13 @@
       <c r="C80" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="E80" s="158" t="s">
+      <c r="E80" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F80" s="160">
+      <c r="F80" s="149">
         <v>11985</v>
       </c>
-      <c r="H80" s="161">
+      <c r="H80" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20704,13 +20701,13 @@
       <c r="C81" s="64">
         <v>11986</v>
       </c>
-      <c r="E81" s="158" t="s">
+      <c r="E81" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F81" s="159">
+      <c r="F81" s="148">
         <v>11986</v>
       </c>
-      <c r="H81" s="161">
+      <c r="H81" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20722,13 +20719,13 @@
       <c r="C82" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E82" s="158" t="s">
+      <c r="E82" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F82" s="159">
+      <c r="F82" s="148">
         <v>11989</v>
       </c>
-      <c r="H82" s="161">
+      <c r="H82" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20740,13 +20737,13 @@
       <c r="C83" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="E83" s="158" t="s">
+      <c r="E83" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F83" s="159">
+      <c r="F83" s="148">
         <v>11990</v>
       </c>
-      <c r="H83" s="161">
+      <c r="H83" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20758,13 +20755,13 @@
       <c r="C84" s="66" t="s">
         <v>169</v>
       </c>
-      <c r="E84" s="158" t="s">
+      <c r="E84" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="F84" s="159">
+      <c r="F84" s="148">
         <v>11996</v>
       </c>
-      <c r="H84" s="161">
+      <c r="H84" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20776,13 +20773,13 @@
       <c r="C85" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="E85" s="158" t="s">
+      <c r="E85" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F85" s="159">
+      <c r="F85" s="148">
         <v>13017</v>
       </c>
-      <c r="H85" s="161">
+      <c r="H85" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20794,13 +20791,13 @@
       <c r="C86" s="64" t="s">
         <v>238</v>
       </c>
-      <c r="E86" s="158" t="s">
+      <c r="E86" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="F86" s="159">
+      <c r="F86" s="148">
         <v>13020</v>
       </c>
-      <c r="H86" s="161">
+      <c r="H86" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20812,13 +20809,13 @@
       <c r="C87" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="E87" s="158" t="s">
+      <c r="E87" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F87" s="159">
+      <c r="F87" s="148">
         <v>13058</v>
       </c>
-      <c r="H87" s="161">
+      <c r="H87" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20830,13 +20827,13 @@
       <c r="C88" s="67" t="s">
         <v>270</v>
       </c>
-      <c r="E88" s="158" t="s">
+      <c r="E88" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F88" s="160">
+      <c r="F88" s="149">
         <v>13070</v>
       </c>
-      <c r="H88" s="161">
+      <c r="H88" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20848,13 +20845,13 @@
       <c r="C89" s="67" t="s">
         <v>326</v>
       </c>
-      <c r="E89" s="158" t="s">
+      <c r="E89" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F89" s="160">
+      <c r="F89" s="149">
         <v>13076</v>
       </c>
-      <c r="H89" s="161">
+      <c r="H89" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20866,13 +20863,13 @@
       <c r="C90" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="E90" s="158" t="s">
+      <c r="E90" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F90" s="160">
+      <c r="F90" s="149">
         <v>13088</v>
       </c>
-      <c r="H90" s="161">
+      <c r="H90" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20884,13 +20881,13 @@
       <c r="C91" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="E91" s="158" t="s">
+      <c r="E91" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="F91" s="159">
+      <c r="F91" s="148">
         <v>13173</v>
       </c>
-      <c r="H91" s="161">
+      <c r="H91" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20902,13 +20899,13 @@
       <c r="C92" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="E92" s="158" t="s">
+      <c r="E92" s="147" t="s">
         <v>266</v>
       </c>
-      <c r="F92" s="159">
+      <c r="F92" s="148">
         <v>13180</v>
       </c>
-      <c r="H92" s="161">
+      <c r="H92" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20920,13 +20917,13 @@
       <c r="C93" s="73" t="s">
         <v>338</v>
       </c>
-      <c r="E93" s="158" t="s">
+      <c r="E93" s="147" t="s">
         <v>307</v>
       </c>
-      <c r="F93" s="160">
+      <c r="F93" s="149">
         <v>13187</v>
       </c>
-      <c r="H93" s="161">
+      <c r="H93" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1D4C6E-C6FB-49BE-9CA1-A415A2B77F8F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD22036-7D49-4D5E-96BF-9708E763BD02}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$BD$94</definedName>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4311" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="594">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1801,9 +1800,6 @@
     <t>Наличие ТВ в магазине на витрине (штуки)</t>
   </si>
   <si>
-    <t>TOP 20</t>
-  </si>
-  <si>
     <t>Количество корзин с надстройками</t>
   </si>
   <si>
@@ -1811,13 +1807,16 @@
   </si>
   <si>
     <t>Количетсво корзин с ассортиментом Кари</t>
+  </si>
+  <si>
+    <t>TOP 15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1903,22 +1902,8 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2027,14 +2012,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="34">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -2425,72 +2404,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2920,22 +2839,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2945,16 +2848,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2969,7 +2863,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2977,14 +2880,7 @@
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <border>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-      </border>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3360,7 +3256,9 @@
     <col min="11" max="11" width="21.21875" style="2" customWidth="1"/>
     <col min="12" max="12" width="18.5546875" style="2" customWidth="1"/>
     <col min="13" max="16" width="15.21875" style="2" customWidth="1"/>
-    <col min="17" max="22" width="16" style="2" customWidth="1"/>
+    <col min="17" max="18" width="16" style="2" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="2" customWidth="1"/>
+    <col min="20" max="22" width="16" style="2" customWidth="1"/>
     <col min="23" max="23" width="29.6640625" style="2" customWidth="1"/>
     <col min="24" max="24" width="38.77734375" style="2" customWidth="1"/>
     <col min="25" max="25" width="64.21875" style="2" customWidth="1"/>
@@ -3381,92 +3279,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="152" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="146" t="s">
         <v>376</v>
       </c>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="152" t="s">
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="146" t="s">
         <v>377</v>
       </c>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="152" t="s">
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="148"/>
+      <c r="U1" s="148"/>
+      <c r="V1" s="153"/>
+      <c r="W1" s="146" t="s">
         <v>378</v>
       </c>
-      <c r="X1" s="154"/>
+      <c r="X1" s="153"/>
       <c r="Y1" s="94" t="s">
         <v>379</v>
       </c>
-      <c r="Z1" s="152" t="s">
+      <c r="Z1" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="152" t="s">
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="146" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="161"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="152" t="s">
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="153"/>
+      <c r="AE1" s="146" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="152" t="s">
+      <c r="AF1" s="153"/>
+      <c r="AG1" s="146" t="s">
         <v>383</v>
       </c>
-      <c r="AH1" s="153"/>
-      <c r="AI1" s="154"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="119" t="s">
         <v>384</v>
       </c>
       <c r="AK1" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="AL1" s="162" t="s">
+      <c r="AL1" s="154" t="s">
         <v>386</v>
       </c>
-      <c r="AM1" s="154"/>
-      <c r="AN1" s="152" t="s">
+      <c r="AM1" s="153"/>
+      <c r="AN1" s="146" t="s">
         <v>387</v>
       </c>
-      <c r="AO1" s="153"/>
-      <c r="AP1" s="155"/>
-      <c r="AQ1" s="162" t="s">
+      <c r="AO1" s="147"/>
+      <c r="AP1" s="148"/>
+      <c r="AQ1" s="154" t="s">
         <v>584</v>
       </c>
-      <c r="AR1" s="152"/>
-      <c r="AS1" s="152"/>
-      <c r="AT1" s="152"/>
-      <c r="AU1" s="153"/>
-      <c r="AV1" s="153"/>
-      <c r="AW1" s="153"/>
-      <c r="AX1" s="154"/>
-      <c r="AY1" s="158" t="s">
+      <c r="AR1" s="146"/>
+      <c r="AS1" s="146"/>
+      <c r="AT1" s="146"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="153"/>
+      <c r="AY1" s="149" t="s">
         <v>388</v>
       </c>
-      <c r="AZ1" s="159"/>
-      <c r="BA1" s="159"/>
-      <c r="BB1" s="159"/>
-      <c r="BC1" s="159"/>
-      <c r="BD1" s="160"/>
+      <c r="AZ1" s="150"/>
+      <c r="BA1" s="150"/>
+      <c r="BB1" s="150"/>
+      <c r="BC1" s="150"/>
+      <c r="BD1" s="151"/>
       <c r="BE1" s="21"/>
     </row>
     <row r="2" spans="1:57" ht="61.8" thickBot="1">
@@ -3495,7 +3393,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="59" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="J2" s="59" t="s">
         <v>370</v>
@@ -3596,17 +3494,17 @@
       <c r="AP2" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="AQ2" s="151" t="s">
+      <c r="AQ2" s="145" t="s">
         <v>25</v>
       </c>
       <c r="AR2" s="84" t="s">
+        <v>590</v>
+      </c>
+      <c r="AS2" s="84" t="s">
         <v>591</v>
       </c>
-      <c r="AS2" s="84" t="s">
+      <c r="AT2" s="84" t="s">
         <v>592</v>
-      </c>
-      <c r="AT2" s="84" t="s">
-        <v>593</v>
       </c>
       <c r="AU2" s="84" t="s">
         <v>359</v>
@@ -4679,7 +4577,9 @@
       <c r="H9" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="64"/>
+      <c r="I9" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J9" s="64" t="s">
         <v>400</v>
       </c>
@@ -4848,7 +4748,9 @@
       <c r="H10" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="64"/>
+      <c r="I10" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J10" s="64" t="s">
         <v>402</v>
       </c>
@@ -5186,7 +5088,9 @@
       <c r="H12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="66"/>
+      <c r="I12" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J12" s="64" t="s">
         <v>405</v>
       </c>
@@ -5353,7 +5257,7 @@
         <v>305</v>
       </c>
       <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
+      <c r="I13" s="64"/>
       <c r="J13" s="64" t="s">
         <v>407</v>
       </c>
@@ -5691,7 +5595,9 @@
       <c r="H15" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="64"/>
+      <c r="I15" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J15" s="64" t="s">
         <v>412</v>
       </c>
@@ -6367,7 +6273,9 @@
       <c r="H19" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I19" s="64"/>
+      <c r="I19" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J19" s="64" t="s">
         <v>420</v>
       </c>
@@ -6536,7 +6444,7 @@
       <c r="H20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="66"/>
+      <c r="I20" s="64"/>
       <c r="J20" s="64" t="s">
         <v>422</v>
       </c>
@@ -6705,7 +6613,7 @@
       <c r="H21" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="66"/>
+      <c r="I21" s="64"/>
       <c r="J21" s="64" t="s">
         <v>424</v>
       </c>
@@ -7210,7 +7118,9 @@
         <v>306</v>
       </c>
       <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
+      <c r="I24" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J24" s="64" t="s">
         <v>431</v>
       </c>
@@ -7374,7 +7284,9 @@
       <c r="H25" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="64"/>
+      <c r="I25" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J25" s="64" t="s">
         <v>432</v>
       </c>
@@ -7543,7 +7455,9 @@
       <c r="H26" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I26" s="64"/>
+      <c r="I26" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J26" s="64" t="s">
         <v>434</v>
       </c>
@@ -7712,7 +7626,9 @@
       <c r="H27" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="64"/>
+      <c r="I27" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J27" s="64" t="s">
         <v>439</v>
       </c>
@@ -7881,7 +7797,7 @@
       <c r="H28" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="I28" s="70"/>
+      <c r="I28" s="64"/>
       <c r="J28" s="64">
         <v>924</v>
       </c>
@@ -8388,7 +8304,9 @@
       <c r="H31" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I31" s="64"/>
+      <c r="I31" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J31" s="64" t="s">
         <v>446</v>
       </c>
@@ -8557,7 +8475,7 @@
       <c r="H32" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="66"/>
+      <c r="I32" s="64"/>
       <c r="J32" s="64" t="s">
         <v>449</v>
       </c>
@@ -9233,7 +9151,9 @@
       <c r="H36" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I36" s="64"/>
+      <c r="I36" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J36" s="64" t="s">
         <v>457</v>
       </c>
@@ -9738,7 +9658,7 @@
         <v>305</v>
       </c>
       <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
+      <c r="I39" s="64"/>
       <c r="J39" s="64" t="s">
         <v>466</v>
       </c>
@@ -10245,7 +10165,7 @@
       <c r="H42" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="66"/>
+      <c r="I42" s="64"/>
       <c r="J42" s="64" t="s">
         <v>474</v>
       </c>
@@ -10412,7 +10332,7 @@
         <v>305</v>
       </c>
       <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
+      <c r="I43" s="64"/>
       <c r="J43" s="64" t="s">
         <v>476</v>
       </c>
@@ -10581,7 +10501,7 @@
       <c r="H44" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="I44" s="66"/>
+      <c r="I44" s="64"/>
       <c r="J44" s="64" t="s">
         <v>478</v>
       </c>
@@ -10914,7 +10834,7 @@
       <c r="H46" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I46" s="66"/>
+      <c r="I46" s="64"/>
       <c r="J46" s="64" t="s">
         <v>482</v>
       </c>
@@ -11421,7 +11341,7 @@
       <c r="H49" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I49" s="66"/>
+      <c r="I49" s="64"/>
       <c r="J49" s="64" t="s">
         <v>489</v>
       </c>
@@ -11757,7 +11677,7 @@
         <v>305</v>
       </c>
       <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
+      <c r="I51" s="64"/>
       <c r="J51" s="64" t="s">
         <v>493</v>
       </c>
@@ -12433,7 +12353,7 @@
       <c r="H55" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I55" s="66"/>
+      <c r="I55" s="64"/>
       <c r="J55" s="64" t="s">
         <v>501</v>
       </c>
@@ -13614,7 +13534,7 @@
         <v>305</v>
       </c>
       <c r="H62" s="68"/>
-      <c r="I62" s="68"/>
+      <c r="I62" s="64"/>
       <c r="J62" s="64" t="s">
         <v>515</v>
       </c>
@@ -13783,7 +13703,7 @@
       <c r="H63" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="I63" s="66"/>
+      <c r="I63" s="64"/>
       <c r="J63" s="64" t="s">
         <v>517</v>
       </c>
@@ -14121,7 +14041,9 @@
       <c r="H65" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="I65" s="64"/>
+      <c r="I65" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J65" s="64" t="s">
         <v>522</v>
       </c>
@@ -14457,7 +14379,7 @@
         <v>305</v>
       </c>
       <c r="H67" s="68"/>
-      <c r="I67" s="68"/>
+      <c r="I67" s="64"/>
       <c r="J67" s="64">
         <v>429.8</v>
       </c>
@@ -14624,7 +14546,7 @@
         <v>305</v>
       </c>
       <c r="H68" s="68"/>
-      <c r="I68" s="68"/>
+      <c r="I68" s="64"/>
       <c r="J68" s="64">
         <v>651</v>
       </c>
@@ -15124,7 +15046,9 @@
         <v>305</v>
       </c>
       <c r="H71" s="68"/>
-      <c r="I71" s="68"/>
+      <c r="I71" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J71" s="64" t="s">
         <v>532</v>
       </c>
@@ -15460,7 +15384,7 @@
         <v>305</v>
       </c>
       <c r="H73" s="68"/>
-      <c r="I73" s="68"/>
+      <c r="I73" s="64"/>
       <c r="J73" s="64" t="s">
         <v>537</v>
       </c>
@@ -15624,7 +15548,7 @@
       <c r="H74" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="I74" s="66"/>
+      <c r="I74" s="64"/>
       <c r="J74" s="64">
         <v>470</v>
       </c>
@@ -15791,7 +15715,7 @@
         <v>305</v>
       </c>
       <c r="H75" s="68"/>
-      <c r="I75" s="68"/>
+      <c r="I75" s="64"/>
       <c r="J75" s="64" t="s">
         <v>540</v>
       </c>
@@ -16124,7 +16048,7 @@
       <c r="H77" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="I77" s="66"/>
+      <c r="I77" s="64"/>
       <c r="J77" s="64" t="s">
         <v>543</v>
       </c>
@@ -16460,7 +16384,7 @@
         <v>305</v>
       </c>
       <c r="H79" s="68"/>
-      <c r="I79" s="68"/>
+      <c r="I79" s="64"/>
       <c r="J79" s="64" t="s">
         <v>549</v>
       </c>
@@ -16629,7 +16553,7 @@
       <c r="H80" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="I80" s="66"/>
+      <c r="I80" s="64"/>
       <c r="J80" s="64" t="s">
         <v>551</v>
       </c>
@@ -16796,7 +16720,7 @@
         <v>305</v>
       </c>
       <c r="H81" s="68"/>
-      <c r="I81" s="68"/>
+      <c r="I81" s="64"/>
       <c r="J81" s="64" t="s">
         <v>554</v>
       </c>
@@ -17303,7 +17227,7 @@
       <c r="H84" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="I84" s="66"/>
+      <c r="I84" s="64"/>
       <c r="J84" s="64" t="s">
         <v>428</v>
       </c>
@@ -17472,7 +17396,9 @@
       <c r="H85" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I85" s="66"/>
+      <c r="I85" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J85" s="64" t="s">
         <v>561</v>
       </c>
@@ -18146,7 +18072,7 @@
         <v>305</v>
       </c>
       <c r="H89" s="68"/>
-      <c r="I89" s="68"/>
+      <c r="I89" s="64"/>
       <c r="J89" s="64" t="s">
         <v>570</v>
       </c>
@@ -18313,7 +18239,7 @@
         <v>305</v>
       </c>
       <c r="H90" s="68"/>
-      <c r="I90" s="68"/>
+      <c r="I90" s="64"/>
       <c r="J90" s="64" t="s">
         <v>572</v>
       </c>
@@ -18480,7 +18406,9 @@
         <v>306</v>
       </c>
       <c r="H91" s="68"/>
-      <c r="I91" s="68"/>
+      <c r="I91" s="64" t="s">
+        <v>593</v>
+      </c>
       <c r="J91" s="64" t="s">
         <v>574</v>
       </c>
@@ -19184,6 +19112,11 @@
     <sortCondition ref="C3:C93"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="AN1:AP1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -19191,64 +19124,59 @@
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AQ1:AX1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C80:C94">
-    <cfRule type="expression" dxfId="11" priority="14">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($B80&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D80:D92">
-    <cfRule type="expression" dxfId="10" priority="13">
+    <cfRule type="expression" dxfId="9" priority="13">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($B80&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E80:E92">
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($B80&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ9 AZ26 AZ71 AZ94 AZ31 BA36 BA91 BB5 BB37:BB39 BC4 BB8 BC7 BB17:BB20 BB22 BB24 BC23 BB28:BB29 BB33 BC30 BB41:BB45 BC40 BB47:BB52 BB54:BB57 BB62:BB64 BB66:BB68 BB70 BB74:BB79 BB81:BB85 BD6 BB11:BB15 BD16 BD27 BB59:BB60 BD46 BD61 BD73 BD86 BB87:BB90 O10 O39 O91 P4 P15 P40 P66 P9 P19 P24 P26:P27 P31:P32 P36 P38 P43 P71 P80 P83 P85:P86 BD65 O65 AY10 AY25 AY92:AY93 AY32 AY21">
-    <cfRule type="containsBlanks" dxfId="8" priority="8">
+    <cfRule type="containsBlanks" dxfId="7" priority="8">
       <formula>LEN(TRIM(O4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34">
-    <cfRule type="containsBlanks" dxfId="7" priority="7">
+    <cfRule type="containsBlanks" dxfId="6" priority="7">
       <formula>LEN(TRIM(BB34))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB35">
-    <cfRule type="containsBlanks" dxfId="6" priority="6">
+    <cfRule type="containsBlanks" dxfId="5" priority="6">
       <formula>LEN(TRIM(BB35))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB53">
-    <cfRule type="containsBlanks" dxfId="5" priority="5">
+    <cfRule type="containsBlanks" dxfId="4" priority="5">
       <formula>LEN(TRIM(BB53))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB58">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+    <cfRule type="containsBlanks" dxfId="3" priority="4">
       <formula>LEN(TRIM(BB58))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB69">
-    <cfRule type="containsBlanks" dxfId="3" priority="3">
+    <cfRule type="containsBlanks" dxfId="2" priority="3">
       <formula>LEN(TRIM(BB69))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD72">
-    <cfRule type="containsBlanks" dxfId="2" priority="2">
+    <cfRule type="containsBlanks" dxfId="1" priority="2">
       <formula>LEN(TRIM(BD72))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD80">
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(BD80))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19260,1681 +19188,4 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4279808A-7649-4142-A200-C32BE7C60633}">
-  <dimension ref="B1:H93"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:8" ht="15" thickBot="1"/>
-    <row r="2" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B2" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="145" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="146">
-        <v>10027</v>
-      </c>
-      <c r="H2" s="150">
-        <f>F2-C2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="15" thickBot="1">
-      <c r="B3" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F3" s="148">
-        <v>10462</v>
-      </c>
-      <c r="H3" s="150">
-        <f t="shared" ref="H3:H66" si="0">F3-C3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1">
-      <c r="B4" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F4" s="148">
-        <v>10541</v>
-      </c>
-      <c r="H4" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15" thickBot="1">
-      <c r="B5" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" s="148">
-        <v>10625</v>
-      </c>
-      <c r="H5" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="15" thickBot="1">
-      <c r="B6" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="148">
-        <v>10696</v>
-      </c>
-      <c r="H6" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15" thickBot="1">
-      <c r="B7" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="148">
-        <v>10777</v>
-      </c>
-      <c r="H7" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="15" thickBot="1">
-      <c r="B8" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C8" s="64" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" s="148">
-        <v>10919</v>
-      </c>
-      <c r="H8" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="15" thickBot="1">
-      <c r="B9" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="148">
-        <v>10949</v>
-      </c>
-      <c r="H9" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="15" thickBot="1">
-      <c r="B10" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" s="148">
-        <v>10951</v>
-      </c>
-      <c r="H10" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="15" thickBot="1">
-      <c r="B11" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="148">
-        <v>11015</v>
-      </c>
-      <c r="H11" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="15" thickBot="1">
-      <c r="B12" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C12" s="67" t="s">
-        <v>336</v>
-      </c>
-      <c r="E12" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F12" s="149">
-        <v>11063</v>
-      </c>
-      <c r="H12" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B13" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="E13" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="148">
-        <v>11103</v>
-      </c>
-      <c r="H13" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="15" thickBot="1">
-      <c r="B14" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="E14" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F14" s="148">
-        <v>11117</v>
-      </c>
-      <c r="H14" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="15" thickBot="1">
-      <c r="B15" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" s="148">
-        <v>11143</v>
-      </c>
-      <c r="H15" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="15" thickBot="1">
-      <c r="B16" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="148">
-        <v>11187</v>
-      </c>
-      <c r="H16" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="15" thickBot="1">
-      <c r="B17" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="E17" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F17" s="148">
-        <v>11340</v>
-      </c>
-      <c r="H17" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="15" thickBot="1">
-      <c r="B18" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="148">
-        <v>11341</v>
-      </c>
-      <c r="H18" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="15" thickBot="1">
-      <c r="B19" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="148">
-        <v>11352</v>
-      </c>
-      <c r="H19" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="15" thickBot="1">
-      <c r="B20" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="148">
-        <v>11372</v>
-      </c>
-      <c r="H20" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="15" thickBot="1">
-      <c r="B21" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="148">
-        <v>11373</v>
-      </c>
-      <c r="H21" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="15" thickBot="1">
-      <c r="B22" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="148">
-        <v>11374</v>
-      </c>
-      <c r="H22" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="15" thickBot="1">
-      <c r="B23" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>335</v>
-      </c>
-      <c r="E23" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F23" s="149">
-        <v>11385</v>
-      </c>
-      <c r="H23" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="15" thickBot="1">
-      <c r="B24" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F24" s="148">
-        <v>11404</v>
-      </c>
-      <c r="H24" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B25" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>291</v>
-      </c>
-      <c r="E25" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F25" s="148">
-        <v>11418</v>
-      </c>
-      <c r="H25" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="15" thickBot="1">
-      <c r="B26" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>228</v>
-      </c>
-      <c r="E26" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F26" s="148">
-        <v>11422</v>
-      </c>
-      <c r="H26" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="15" thickBot="1">
-      <c r="B27" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="148">
-        <v>11424</v>
-      </c>
-      <c r="H27" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B28" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" s="64" t="s">
-        <v>296</v>
-      </c>
-      <c r="E28" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F28" s="148">
-        <v>11433</v>
-      </c>
-      <c r="H28" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="15" thickBot="1">
-      <c r="B29" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C29" s="64" t="s">
-        <v>243</v>
-      </c>
-      <c r="E29" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F29" s="148">
-        <v>11435</v>
-      </c>
-      <c r="H29" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="15" thickBot="1">
-      <c r="B30" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="148">
-        <v>11437</v>
-      </c>
-      <c r="H30" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="15" thickBot="1">
-      <c r="B31" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" s="148">
-        <v>11439</v>
-      </c>
-      <c r="H31" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="15" thickBot="1">
-      <c r="B32" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="148">
-        <v>11448</v>
-      </c>
-      <c r="H32" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="15" thickBot="1">
-      <c r="B33" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>246</v>
-      </c>
-      <c r="E33" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F33" s="148">
-        <v>11455</v>
-      </c>
-      <c r="H33" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B34" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F34" s="148">
-        <v>11464</v>
-      </c>
-      <c r="H34" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B35" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>294</v>
-      </c>
-      <c r="E35" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" s="148">
-        <v>11472</v>
-      </c>
-      <c r="H35" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="15" thickBot="1">
-      <c r="B36" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C36" s="64" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F36" s="148">
-        <v>11490</v>
-      </c>
-      <c r="H36" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="15" thickBot="1">
-      <c r="B37" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="148">
-        <v>11495</v>
-      </c>
-      <c r="H37" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="15" thickBot="1">
-      <c r="B38" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C38" s="67" t="s">
-        <v>329</v>
-      </c>
-      <c r="E38" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F38" s="149">
-        <v>11501</v>
-      </c>
-      <c r="H38" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="15" thickBot="1">
-      <c r="B39" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="E39" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F39" s="148">
-        <v>11509</v>
-      </c>
-      <c r="H39" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="15" thickBot="1">
-      <c r="B40" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C40" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F40" s="148">
-        <v>11515</v>
-      </c>
-      <c r="H40" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="15" thickBot="1">
-      <c r="B41" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" s="148">
-        <v>11518</v>
-      </c>
-      <c r="H41" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="15" thickBot="1">
-      <c r="B42" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C42" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="E42" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F42" s="149">
-        <v>11521</v>
-      </c>
-      <c r="H42" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="15" thickBot="1">
-      <c r="B43" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" s="66" t="s">
-        <v>158</v>
-      </c>
-      <c r="E43" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F43" s="148">
-        <v>11523</v>
-      </c>
-      <c r="H43" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="15" thickBot="1">
-      <c r="B44" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C44" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="E44" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="148">
-        <v>11525</v>
-      </c>
-      <c r="H44" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="15" thickBot="1">
-      <c r="B45" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="E45" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F45" s="148">
-        <v>11529</v>
-      </c>
-      <c r="H45" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" thickBot="1">
-      <c r="B46" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C46" s="64" t="s">
-        <v>252</v>
-      </c>
-      <c r="E46" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F46" s="148">
-        <v>11534</v>
-      </c>
-      <c r="H46" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B47" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C47" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F47" s="148">
-        <v>11557</v>
-      </c>
-      <c r="H47" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="15" thickBot="1">
-      <c r="B48" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="66" t="s">
-        <v>137</v>
-      </c>
-      <c r="E48" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" s="148">
-        <v>11567</v>
-      </c>
-      <c r="H48" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="15" thickBot="1">
-      <c r="B49" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F49" s="148">
-        <v>11571</v>
-      </c>
-      <c r="H49" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" ht="15" thickBot="1">
-      <c r="B50" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C50" s="67" t="s">
-        <v>325</v>
-      </c>
-      <c r="E50" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F50" s="149">
-        <v>11605</v>
-      </c>
-      <c r="H50" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="15" thickBot="1">
-      <c r="B51" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="E51" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="148">
-        <v>11621</v>
-      </c>
-      <c r="H51" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B52" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C52" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="E52" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F52" s="148">
-        <v>11627</v>
-      </c>
-      <c r="H52" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B53" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C53" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F53" s="148">
-        <v>11639</v>
-      </c>
-      <c r="H53" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="15" thickBot="1">
-      <c r="B54" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="E54" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="148">
-        <v>11647</v>
-      </c>
-      <c r="H54" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B55" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C55" s="64" t="s">
-        <v>278</v>
-      </c>
-      <c r="E55" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F55" s="148">
-        <v>11658</v>
-      </c>
-      <c r="H55" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B56" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C56" s="64" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56" s="148">
-        <v>11703</v>
-      </c>
-      <c r="H56" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B57" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C57" s="64" t="s">
-        <v>285</v>
-      </c>
-      <c r="E57" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F57" s="148">
-        <v>11708</v>
-      </c>
-      <c r="H57" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" ht="15" thickBot="1">
-      <c r="B58" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C58" s="64" t="s">
-        <v>236</v>
-      </c>
-      <c r="E58" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F58" s="148">
-        <v>11729</v>
-      </c>
-      <c r="H58" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" ht="15" thickBot="1">
-      <c r="B59" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="E59" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F59" s="148">
-        <v>11731</v>
-      </c>
-      <c r="H59" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" ht="15" thickBot="1">
-      <c r="B60" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C60" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F60" s="148">
-        <v>11735</v>
-      </c>
-      <c r="H60" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" ht="15" thickBot="1">
-      <c r="B61" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C61" s="67" t="s">
-        <v>330</v>
-      </c>
-      <c r="E61" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F61" s="149">
-        <v>11759</v>
-      </c>
-      <c r="H61" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" ht="15" thickBot="1">
-      <c r="B62" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="E62" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F62" s="148">
-        <v>11760</v>
-      </c>
-      <c r="H62" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" ht="15" thickBot="1">
-      <c r="B63" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C63" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F63" s="148">
-        <v>11807</v>
-      </c>
-      <c r="H63" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B64" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C64" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="E64" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F64" s="148">
-        <v>11813</v>
-      </c>
-      <c r="H64" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" ht="15" thickBot="1">
-      <c r="B65" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C65" s="64" t="s">
-        <v>48</v>
-      </c>
-      <c r="E65" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F65" s="148">
-        <v>11823</v>
-      </c>
-      <c r="H65" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" ht="15" thickBot="1">
-      <c r="B66" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C66" s="67" t="s">
-        <v>328</v>
-      </c>
-      <c r="E66" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F66" s="149">
-        <v>11828</v>
-      </c>
-      <c r="H66" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" ht="15" thickBot="1">
-      <c r="B67" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C67" s="67" t="s">
-        <v>268</v>
-      </c>
-      <c r="E67" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F67" s="149">
-        <v>11829</v>
-      </c>
-      <c r="H67" s="150">
-        <f t="shared" ref="H67:H93" si="1">F67-C67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" ht="15" thickBot="1">
-      <c r="B68" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="E68" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F68" s="148">
-        <v>11836</v>
-      </c>
-      <c r="H68" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B69" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C69" s="64" t="s">
-        <v>283</v>
-      </c>
-      <c r="E69" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F69" s="148">
-        <v>11839</v>
-      </c>
-      <c r="H69" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" ht="15" thickBot="1">
-      <c r="B70" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C70" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="E70" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F70" s="149">
-        <v>11843</v>
-      </c>
-      <c r="H70" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" ht="15" thickBot="1">
-      <c r="B71" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E71" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F71" s="148">
-        <v>11854</v>
-      </c>
-      <c r="H71" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" ht="15" thickBot="1">
-      <c r="B72" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C72" s="67" t="s">
-        <v>327</v>
-      </c>
-      <c r="E72" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F72" s="149">
-        <v>11855</v>
-      </c>
-      <c r="H72" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="15" thickBot="1">
-      <c r="B73" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C73" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="E73" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F73" s="148">
-        <v>11861</v>
-      </c>
-      <c r="H73" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" ht="15" thickBot="1">
-      <c r="B74" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C74" s="67" t="s">
-        <v>331</v>
-      </c>
-      <c r="E74" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F74" s="149">
-        <v>11875</v>
-      </c>
-      <c r="H74" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B75" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C75" s="64" t="s">
-        <v>275</v>
-      </c>
-      <c r="E75" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F75" s="148">
-        <v>11877</v>
-      </c>
-      <c r="H75" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8" ht="15" thickBot="1">
-      <c r="B76" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>188</v>
-      </c>
-      <c r="E76" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F76" s="148">
-        <v>11898</v>
-      </c>
-      <c r="H76" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8" ht="15" thickBot="1">
-      <c r="B77" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C77" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="E77" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F77" s="148">
-        <v>11900</v>
-      </c>
-      <c r="H77" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="15" thickBot="1">
-      <c r="B78" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C78" s="67" t="s">
-        <v>332</v>
-      </c>
-      <c r="E78" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F78" s="149">
-        <v>11906</v>
-      </c>
-      <c r="H78" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="15" thickBot="1">
-      <c r="B79" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C79" s="66" t="s">
-        <v>149</v>
-      </c>
-      <c r="E79" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F79" s="148">
-        <v>11974</v>
-      </c>
-      <c r="H79" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" ht="15" thickBot="1">
-      <c r="B80" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C80" s="67" t="s">
-        <v>324</v>
-      </c>
-      <c r="E80" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F80" s="149">
-        <v>11985</v>
-      </c>
-      <c r="H80" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" ht="15" thickBot="1">
-      <c r="B81" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" s="64">
-        <v>11986</v>
-      </c>
-      <c r="E81" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F81" s="148">
-        <v>11986</v>
-      </c>
-      <c r="H81" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" ht="15" thickBot="1">
-      <c r="B82" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C82" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="E82" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F82" s="148">
-        <v>11989</v>
-      </c>
-      <c r="H82" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" ht="15" thickBot="1">
-      <c r="B83" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C83" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="E83" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F83" s="148">
-        <v>11990</v>
-      </c>
-      <c r="H83" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" ht="15" thickBot="1">
-      <c r="B84" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="C84" s="66" t="s">
-        <v>169</v>
-      </c>
-      <c r="E84" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="F84" s="148">
-        <v>11996</v>
-      </c>
-      <c r="H84" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8" ht="15" thickBot="1">
-      <c r="B85" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C85" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="E85" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F85" s="148">
-        <v>13017</v>
-      </c>
-      <c r="H85" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" thickBot="1">
-      <c r="B86" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C86" s="64" t="s">
-        <v>238</v>
-      </c>
-      <c r="E86" s="147" t="s">
-        <v>226</v>
-      </c>
-      <c r="F86" s="148">
-        <v>13020</v>
-      </c>
-      <c r="H86" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8" ht="15" thickBot="1">
-      <c r="B87" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C87" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="E87" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F87" s="148">
-        <v>13058</v>
-      </c>
-      <c r="H87" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" ht="15" thickBot="1">
-      <c r="B88" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C88" s="67" t="s">
-        <v>270</v>
-      </c>
-      <c r="E88" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F88" s="149">
-        <v>13070</v>
-      </c>
-      <c r="H88" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8" ht="15" thickBot="1">
-      <c r="B89" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C89" s="67" t="s">
-        <v>326</v>
-      </c>
-      <c r="E89" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F89" s="149">
-        <v>13076</v>
-      </c>
-      <c r="H89" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" ht="15" thickBot="1">
-      <c r="B90" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="C90" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="E90" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F90" s="149">
-        <v>13088</v>
-      </c>
-      <c r="H90" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" ht="15" thickBot="1">
-      <c r="B91" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C91" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="E91" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="F91" s="148">
-        <v>13173</v>
-      </c>
-      <c r="H91" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8" ht="22.2" thickBot="1">
-      <c r="B92" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C92" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="E92" s="147" t="s">
-        <v>266</v>
-      </c>
-      <c r="F92" s="148">
-        <v>13180</v>
-      </c>
-      <c r="H92" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8" ht="15" thickBot="1">
-      <c r="B93" s="72" t="s">
-        <v>307</v>
-      </c>
-      <c r="C93" s="73" t="s">
-        <v>338</v>
-      </c>
-      <c r="E93" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="F93" s="149">
-        <v>13187</v>
-      </c>
-      <c r="H93" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C79:C93">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IF(ROW()&gt;4,IF(AND(#REF!=1,OR($B79&lt;&gt;"",#REF!&lt;&gt;"")),TRUE(),FALSE()),FALSE())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD22036-7D49-4D5E-96BF-9708E763BD02}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADBD645-76A9-41B3-8043-C30DC4D47583}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2848,7 +2848,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2863,16 +2872,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3279,75 +3279,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="150" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="156"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="146" t="s">
         <v>376</v>
       </c>
       <c r="N1" s="147"/>
       <c r="O1" s="147"/>
-      <c r="P1" s="153"/>
+      <c r="P1" s="148"/>
       <c r="Q1" s="146" t="s">
         <v>377</v>
       </c>
       <c r="R1" s="147"/>
       <c r="S1" s="147"/>
-      <c r="T1" s="148"/>
-      <c r="U1" s="148"/>
-      <c r="V1" s="153"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="148"/>
       <c r="W1" s="146" t="s">
         <v>378</v>
       </c>
-      <c r="X1" s="153"/>
+      <c r="X1" s="148"/>
       <c r="Y1" s="94" t="s">
         <v>379</v>
       </c>
       <c r="Z1" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="153"/>
+      <c r="AA1" s="148"/>
       <c r="AB1" s="146" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="152"/>
-      <c r="AD1" s="153"/>
+      <c r="AC1" s="155"/>
+      <c r="AD1" s="148"/>
       <c r="AE1" s="146" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="153"/>
+      <c r="AF1" s="148"/>
       <c r="AG1" s="146" t="s">
         <v>383</v>
       </c>
       <c r="AH1" s="147"/>
-      <c r="AI1" s="153"/>
+      <c r="AI1" s="148"/>
       <c r="AJ1" s="119" t="s">
         <v>384</v>
       </c>
       <c r="AK1" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="AL1" s="154" t="s">
+      <c r="AL1" s="156" t="s">
         <v>386</v>
       </c>
-      <c r="AM1" s="153"/>
+      <c r="AM1" s="148"/>
       <c r="AN1" s="146" t="s">
         <v>387</v>
       </c>
       <c r="AO1" s="147"/>
-      <c r="AP1" s="148"/>
-      <c r="AQ1" s="154" t="s">
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="156" t="s">
         <v>584</v>
       </c>
       <c r="AR1" s="146"/>
@@ -3356,15 +3356,15 @@
       <c r="AU1" s="147"/>
       <c r="AV1" s="147"/>
       <c r="AW1" s="147"/>
-      <c r="AX1" s="153"/>
-      <c r="AY1" s="149" t="s">
+      <c r="AX1" s="148"/>
+      <c r="AY1" s="152" t="s">
         <v>388</v>
       </c>
-      <c r="AZ1" s="150"/>
-      <c r="BA1" s="150"/>
-      <c r="BB1" s="150"/>
-      <c r="BC1" s="150"/>
-      <c r="BD1" s="151"/>
+      <c r="AZ1" s="153"/>
+      <c r="BA1" s="153"/>
+      <c r="BB1" s="153"/>
+      <c r="BC1" s="153"/>
+      <c r="BD1" s="154"/>
       <c r="BE1" s="21"/>
     </row>
     <row r="2" spans="1:57" ht="61.8" thickBot="1">
@@ -5256,7 +5256,9 @@
       <c r="G13" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H13" s="68"/>
+      <c r="H13" s="68">
+        <v>3</v>
+      </c>
       <c r="I13" s="64"/>
       <c r="J13" s="64" t="s">
         <v>407</v>
@@ -7117,7 +7119,9 @@
       <c r="G24" s="65" t="s">
         <v>306</v>
       </c>
-      <c r="H24" s="68"/>
+      <c r="H24" s="68">
+        <v>5</v>
+      </c>
       <c r="I24" s="64" t="s">
         <v>593</v>
       </c>
@@ -9657,7 +9661,9 @@
       <c r="G39" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H39" s="68"/>
+      <c r="H39" s="68">
+        <v>1</v>
+      </c>
       <c r="I39" s="64"/>
       <c r="J39" s="64" t="s">
         <v>466</v>
@@ -10331,7 +10337,9 @@
       <c r="G43" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H43" s="68"/>
+      <c r="H43" s="68">
+        <v>3</v>
+      </c>
       <c r="I43" s="64"/>
       <c r="J43" s="64" t="s">
         <v>476</v>
@@ -11676,7 +11684,9 @@
       <c r="G51" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H51" s="68"/>
+      <c r="H51" s="68">
+        <v>3</v>
+      </c>
       <c r="I51" s="64"/>
       <c r="J51" s="64" t="s">
         <v>493</v>
@@ -13533,7 +13543,9 @@
       <c r="G62" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H62" s="68"/>
+      <c r="H62" s="68">
+        <v>3</v>
+      </c>
       <c r="I62" s="64"/>
       <c r="J62" s="64" t="s">
         <v>515</v>
@@ -14378,7 +14390,9 @@
       <c r="G67" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H67" s="68"/>
+      <c r="H67" s="68">
+        <v>2</v>
+      </c>
       <c r="I67" s="64"/>
       <c r="J67" s="64">
         <v>429.8</v>
@@ -14545,7 +14559,9 @@
       <c r="G68" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H68" s="68"/>
+      <c r="H68" s="68">
+        <v>1</v>
+      </c>
       <c r="I68" s="64"/>
       <c r="J68" s="64">
         <v>651</v>
@@ -15045,7 +15061,9 @@
       <c r="G71" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H71" s="68"/>
+      <c r="H71" s="68">
+        <v>5</v>
+      </c>
       <c r="I71" s="64" t="s">
         <v>593</v>
       </c>
@@ -15383,7 +15401,9 @@
       <c r="G73" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H73" s="68"/>
+      <c r="H73" s="68">
+        <v>3</v>
+      </c>
       <c r="I73" s="64"/>
       <c r="J73" s="64" t="s">
         <v>537</v>
@@ -15714,7 +15734,9 @@
       <c r="G75" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H75" s="68"/>
+      <c r="H75" s="68">
+        <v>3</v>
+      </c>
       <c r="I75" s="64"/>
       <c r="J75" s="64" t="s">
         <v>540</v>
@@ -16383,7 +16405,9 @@
       <c r="G79" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H79" s="68"/>
+      <c r="H79" s="68">
+        <v>3</v>
+      </c>
       <c r="I79" s="64"/>
       <c r="J79" s="64" t="s">
         <v>549</v>
@@ -16719,7 +16743,9 @@
       <c r="G81" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H81" s="68"/>
+      <c r="H81" s="68">
+        <v>1</v>
+      </c>
       <c r="I81" s="64"/>
       <c r="J81" s="64" t="s">
         <v>554</v>
@@ -18071,7 +18097,9 @@
       <c r="G89" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H89" s="68"/>
+      <c r="H89" s="68">
+        <v>1</v>
+      </c>
       <c r="I89" s="64"/>
       <c r="J89" s="64" t="s">
         <v>570</v>
@@ -18238,7 +18266,9 @@
       <c r="G90" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="H90" s="68"/>
+      <c r="H90" s="68">
+        <v>1</v>
+      </c>
       <c r="I90" s="64"/>
       <c r="J90" s="64" t="s">
         <v>572</v>
@@ -18405,7 +18435,9 @@
       <c r="G91" s="65" t="s">
         <v>306</v>
       </c>
-      <c r="H91" s="68"/>
+      <c r="H91" s="68">
+        <v>5</v>
+      </c>
       <c r="I91" s="64" t="s">
         <v>593</v>
       </c>
@@ -18907,7 +18939,9 @@
       <c r="G94" s="74" t="s">
         <v>305</v>
       </c>
-      <c r="H94" s="75"/>
+      <c r="H94" s="75">
+        <v>4</v>
+      </c>
       <c r="I94" s="75"/>
       <c r="J94" s="72" t="s">
         <v>581</v>
@@ -19112,11 +19146,6 @@
     <sortCondition ref="C3:C93"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="AN1:AP1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -19124,6 +19153,11 @@
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AQ1:AX1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C80:C94">
     <cfRule type="expression" dxfId="10" priority="14">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADBD645-76A9-41B3-8043-C30DC4D47583}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D8EDA7-9492-41B4-B8E4-B13131FF178A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="595">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1810,6 +1810,9 @@
   </si>
   <si>
     <t>TOP 15</t>
+  </si>
+  <si>
+    <t>home,sport</t>
   </si>
 </sst>
 </file>
@@ -2848,16 +2851,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2872,7 +2866,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3279,75 +3282,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="155" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="151"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="156"/>
       <c r="M1" s="146" t="s">
         <v>376</v>
       </c>
       <c r="N1" s="147"/>
       <c r="O1" s="147"/>
-      <c r="P1" s="148"/>
+      <c r="P1" s="153"/>
       <c r="Q1" s="146" t="s">
         <v>377</v>
       </c>
       <c r="R1" s="147"/>
       <c r="S1" s="147"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="148"/>
+      <c r="T1" s="148"/>
+      <c r="U1" s="148"/>
+      <c r="V1" s="153"/>
       <c r="W1" s="146" t="s">
         <v>378</v>
       </c>
-      <c r="X1" s="148"/>
+      <c r="X1" s="153"/>
       <c r="Y1" s="94" t="s">
         <v>379</v>
       </c>
       <c r="Z1" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="148"/>
+      <c r="AA1" s="153"/>
       <c r="AB1" s="146" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="148"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="153"/>
       <c r="AE1" s="146" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="148"/>
+      <c r="AF1" s="153"/>
       <c r="AG1" s="146" t="s">
         <v>383</v>
       </c>
       <c r="AH1" s="147"/>
-      <c r="AI1" s="148"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="119" t="s">
         <v>384</v>
       </c>
       <c r="AK1" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="AL1" s="156" t="s">
+      <c r="AL1" s="154" t="s">
         <v>386</v>
       </c>
-      <c r="AM1" s="148"/>
+      <c r="AM1" s="153"/>
       <c r="AN1" s="146" t="s">
         <v>387</v>
       </c>
       <c r="AO1" s="147"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="156" t="s">
+      <c r="AP1" s="148"/>
+      <c r="AQ1" s="154" t="s">
         <v>584</v>
       </c>
       <c r="AR1" s="146"/>
@@ -3356,15 +3359,15 @@
       <c r="AU1" s="147"/>
       <c r="AV1" s="147"/>
       <c r="AW1" s="147"/>
-      <c r="AX1" s="148"/>
-      <c r="AY1" s="152" t="s">
+      <c r="AX1" s="153"/>
+      <c r="AY1" s="149" t="s">
         <v>388</v>
       </c>
-      <c r="AZ1" s="153"/>
-      <c r="BA1" s="153"/>
-      <c r="BB1" s="153"/>
-      <c r="BC1" s="153"/>
-      <c r="BD1" s="154"/>
+      <c r="AZ1" s="150"/>
+      <c r="BA1" s="150"/>
+      <c r="BB1" s="150"/>
+      <c r="BC1" s="150"/>
+      <c r="BD1" s="151"/>
       <c r="BE1" s="21"/>
     </row>
     <row r="2" spans="1:57" ht="61.8" thickBot="1">
@@ -11429,7 +11432,7 @@
         <v>139</v>
       </c>
       <c r="AJ49" s="92" t="s">
-        <v>27</v>
+        <v>594</v>
       </c>
       <c r="AK49" s="92" t="s">
         <v>27</v>
@@ -19146,6 +19149,11 @@
     <sortCondition ref="C3:C93"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="AN1:AP1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -19153,11 +19161,6 @@
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AQ1:AX1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C80:C94">
     <cfRule type="expression" dxfId="10" priority="14">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D8EDA7-9492-41B4-B8E4-B13131FF178A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C7239C-3ED7-4CE5-BC72-402DFA960338}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1840,28 +1840,35 @@
       <sz val="8"/>
       <color indexed="63"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1880,11 +1887,15 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2851,7 +2862,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2866,16 +2886,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3282,75 +3293,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="60.6" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="150" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="156"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="146" t="s">
         <v>376</v>
       </c>
       <c r="N1" s="147"/>
       <c r="O1" s="147"/>
-      <c r="P1" s="153"/>
+      <c r="P1" s="148"/>
       <c r="Q1" s="146" t="s">
         <v>377</v>
       </c>
       <c r="R1" s="147"/>
       <c r="S1" s="147"/>
-      <c r="T1" s="148"/>
-      <c r="U1" s="148"/>
-      <c r="V1" s="153"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="148"/>
       <c r="W1" s="146" t="s">
         <v>378</v>
       </c>
-      <c r="X1" s="153"/>
+      <c r="X1" s="148"/>
       <c r="Y1" s="94" t="s">
         <v>379</v>
       </c>
       <c r="Z1" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="153"/>
+      <c r="AA1" s="148"/>
       <c r="AB1" s="146" t="s">
         <v>381</v>
       </c>
-      <c r="AC1" s="152"/>
-      <c r="AD1" s="153"/>
+      <c r="AC1" s="155"/>
+      <c r="AD1" s="148"/>
       <c r="AE1" s="146" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="153"/>
+      <c r="AF1" s="148"/>
       <c r="AG1" s="146" t="s">
         <v>383</v>
       </c>
       <c r="AH1" s="147"/>
-      <c r="AI1" s="153"/>
+      <c r="AI1" s="148"/>
       <c r="AJ1" s="119" t="s">
         <v>384</v>
       </c>
       <c r="AK1" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="AL1" s="154" t="s">
+      <c r="AL1" s="156" t="s">
         <v>386</v>
       </c>
-      <c r="AM1" s="153"/>
+      <c r="AM1" s="148"/>
       <c r="AN1" s="146" t="s">
         <v>387</v>
       </c>
       <c r="AO1" s="147"/>
-      <c r="AP1" s="148"/>
-      <c r="AQ1" s="154" t="s">
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="156" t="s">
         <v>584</v>
       </c>
       <c r="AR1" s="146"/>
@@ -3359,15 +3370,15 @@
       <c r="AU1" s="147"/>
       <c r="AV1" s="147"/>
       <c r="AW1" s="147"/>
-      <c r="AX1" s="153"/>
-      <c r="AY1" s="149" t="s">
+      <c r="AX1" s="148"/>
+      <c r="AY1" s="152" t="s">
         <v>388</v>
       </c>
-      <c r="AZ1" s="150"/>
-      <c r="BA1" s="150"/>
-      <c r="BB1" s="150"/>
-      <c r="BC1" s="150"/>
-      <c r="BD1" s="151"/>
+      <c r="AZ1" s="153"/>
+      <c r="BA1" s="153"/>
+      <c r="BB1" s="153"/>
+      <c r="BC1" s="153"/>
+      <c r="BD1" s="154"/>
       <c r="BE1" s="21"/>
     </row>
     <row r="2" spans="1:57" ht="61.8" thickBot="1">
@@ -7987,7 +7998,7 @@
         <v>27</v>
       </c>
       <c r="N29" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>27</v>
@@ -8035,7 +8046,7 @@
         <v>152</v>
       </c>
       <c r="AD29" s="46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE29" s="112" t="s">
         <v>27</v>
@@ -19149,11 +19160,6 @@
     <sortCondition ref="C3:C93"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="AN1:AP1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -19161,6 +19167,11 @@
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AQ1:AX1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="C80:C94">
     <cfRule type="expression" dxfId="10" priority="14">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C7239C-3ED7-4CE5-BC72-402DFA960338}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84207276-58BB-41CF-B06B-8A594CB87C40}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="596">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1813,6 +1813,9 @@
   </si>
   <si>
     <t>home,sport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кидс,спорт </t>
   </si>
 </sst>
 </file>
@@ -5831,20 +5834,20 @@
       <c r="Y16" s="92">
         <v>8</v>
       </c>
-      <c r="Z16" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA16" s="54">
-        <v>35.5</v>
+      <c r="Z16" s="101" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA16" s="101" t="s">
+        <v>27</v>
       </c>
       <c r="AB16" s="108" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC16" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD16" s="46">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="AC16" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD16" s="108" t="s">
+        <v>27</v>
       </c>
       <c r="AE16" s="112" t="s">
         <v>152</v>
@@ -5862,7 +5865,7 @@
         <v>151</v>
       </c>
       <c r="AJ16" s="92" t="s">
-        <v>195</v>
+        <v>595</v>
       </c>
       <c r="AK16" s="92">
         <v>2</v>
@@ -6194,7 +6197,7 @@
         <v>152</v>
       </c>
       <c r="AH18" s="26">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI18" s="41" t="s">
         <v>151</v>
@@ -7668,11 +7671,11 @@
       <c r="P27" s="127">
         <v>10</v>
       </c>
-      <c r="Q27" s="124" t="s">
-        <v>152</v>
-      </c>
-      <c r="R27" s="6">
-        <v>12</v>
+      <c r="Q27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>27</v>
@@ -7856,7 +7859,7 @@
         <v>27</v>
       </c>
       <c r="W28" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28" s="11" t="s">
         <v>170</v>
@@ -7883,13 +7886,13 @@
         <v>152</v>
       </c>
       <c r="AF28" s="44">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG28" s="117" t="s">
         <v>152</v>
       </c>
       <c r="AH28" s="26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI28" s="41" t="s">
         <v>151</v>
@@ -9688,11 +9691,11 @@
       <c r="L39" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M39" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N39" s="2">
-        <v>8</v>
+      <c r="M39" s="7">
+        <v>9</v>
+      </c>
+      <c r="N39" s="37" t="s">
+        <v>27</v>
       </c>
       <c r="O39" s="18">
         <v>8</v>
@@ -9788,7 +9791,7 @@
         <v>2</v>
       </c>
       <c r="AT39" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU39" s="2">
         <v>3</v>
@@ -9861,7 +9864,7 @@
         <v>27</v>
       </c>
       <c r="N40" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>27</v>
@@ -9900,7 +9903,7 @@
         <v>152</v>
       </c>
       <c r="AA40" s="54">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB40" s="108" t="s">
         <v>152</v>
@@ -9915,13 +9918,13 @@
         <v>152</v>
       </c>
       <c r="AF40" s="44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG40" s="117" t="s">
         <v>152</v>
       </c>
       <c r="AH40" s="26">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AI40" s="41" t="s">
         <v>151</v>
@@ -9939,7 +9942,7 @@
         <v>27</v>
       </c>
       <c r="AN40" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO40" s="2" t="s">
         <v>196</v>
@@ -14851,17 +14854,17 @@
       <c r="AR69" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AS69" s="2">
-        <v>1</v>
+      <c r="AS69" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="AT69" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AU69" s="2">
-        <v>2</v>
-      </c>
-      <c r="AV69" s="2">
-        <v>2</v>
+      <c r="AU69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV69" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="AW69" s="2">
         <v>1</v>
@@ -19229,7 +19232,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BD65 AY92:AY93 AW87 AY10 AY21 AY25 AY32 AZ94 AZ9 AZ26 AZ31 AZ71 BA91 BA36 BB87:BB90 BB5 BB8 BB11:BB15 BB17:BB20 BB22 BB24 BB28:BB29 BB33:BB35 BB37:BB39 BB41:BB45 BB47:BB60 BB62:BB64 BB66:BB70 BB74:BB79 BB81:BB85 BD80 BC4 BC7 AW73 BC23 BC30 AW83 BC40 AX80 AW85 AX65 BD72:BD73 BD86 BD6 BD16 BD27 BD46 AX77 BD61 O91 O10 O39 P4 P9 P15 P19 P24 P26:P27 P31:P32 P36 P38 P40 P43 P66 P71 P80 P83 P85:P86 O65 AU3:AU5 AU7:AU18 AU31:AU57 AU60:AU65 AV92:AV93 AV6:AV8 AV10:AV14 AV16:AV18 AU20:AV29 AV31:AV33 AV35:AV38 AV40:AV46 AV48:AV58 AV60:AV63 AV65 AU67:AU94 AV67:AV76 AV78:AV85 AV87:AV89 AW15:AW18 AV3:AW3 AX24 AW5:AW8 AX12 AX28 AX36 AW52:AW57 AX46 AW11:AW13 AW20:AW24 AW26:AW29 AX26 AW31:AW38 AX31 AW40:AW50 AX40 AW60:AW71 AW75:AW78 AW80:AW81 AW89:AW94 AX91" xr:uid="{A4FFEF95-B930-418D-AC80-C6F1FD5FE0CE}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BD65 AY92:AY93 AW87 AY10 AY21 AY25 AY32 AZ94 AZ9 AZ26 AZ31 AZ71 BA91 BA36 BB87:BB90 BB5 BB8 BB11:BB15 BB17:BB20 BB22 BB24 BB28:BB29 BB33:BB35 BB37:BB39 BB41:BB45 BB47:BB60 BB62:BB64 BB66:BB70 BB74:BB79 BB81:BB85 BD80 BC4 BC7 AW73 BC23 BC30 AW83 BC40 AX80 AW85 AX65 BD72:BD73 BD86 BD6 BD16 BD27 BD46 AX77 BD61 O91 O10 O39 P4 P9 P15 P19 P24 P26:P27 P31:P32 P36 P38 P40 P43 P66 P71 P80 P83 P85:P86 O65 AU3:AU5 AU7:AU18 AU31:AU57 AU60:AU65 AV92:AV93 AV6:AV8 AV10:AV14 AV16:AV18 AU20:AV29 AV31:AV33 AV35:AV38 AV40:AV46 AV48:AV58 AV60:AV63 AV65 AX91 AU70:AU94 AV78:AV85 AV87:AV89 AW15:AW18 AV3:AW3 AX24 AW5:AW8 AX12 AX28 AX36 AW52:AW57 AX46 AW11:AW13 AW20:AW24 AW26:AW29 AX26 AW31:AW38 AX31 AW40:AW50 AX40 AW60:AW71 AW75:AW78 AW80:AW81 AW89:AW94 AU67:AV68 AV70:AV76" xr:uid="{A4FFEF95-B930-418D-AC80-C6F1FD5FE0CE}">
       <formula1>"0,1,10,12,14,16,18,2,3,4,5,6,7,8,9,да,нет"</formula1>
     </dataValidation>
   </dataValidations>
